--- a/ExcelToJSONConverter/excel/castle.xlsx
+++ b/ExcelToJSONConverter/excel/castle.xlsx
@@ -3,14 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EC190E-C4A0-4DCF-A3C7-2C055C0A014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8AA5FF-A301-478E-93AF-1E24F4C2AC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1245" yWindow="1065" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Castle" sheetId="4" r:id="rId2"/>
     <sheet name="CastleRise" sheetId="3" r:id="rId3"/>
+    <sheet name="CastleMission" sheetId="5" r:id="rId4"/>
+    <sheet name="CastleMissionReward" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="93">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,13 +164,195 @@
   </si>
   <si>
     <t>Strength</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>#mission_name</t>
+  </si>
+  <si>
+    <t>req_stat_type</t>
+  </si>
+  <si>
+    <t>relic_key</t>
+  </si>
+  <si>
+    <t>varchar(50)</t>
+  </si>
+  <si>
+    <t>military_training</t>
+  </si>
+  <si>
+    <t>군사 훈련 지휘</t>
+  </si>
+  <si>
+    <t>leadership</t>
+  </si>
+  <si>
+    <t>rally_remnants</t>
+  </si>
+  <si>
+    <t>패잔병 수습</t>
+  </si>
+  <si>
+    <t>bandit_subjugation</t>
+  </si>
+  <si>
+    <t>산적 토벌</t>
+  </si>
+  <si>
+    <t>strength</t>
+  </si>
+  <si>
+    <t>border_defense</t>
+  </si>
+  <si>
+    <t>변경 수비</t>
+  </si>
+  <si>
+    <t>tax_reform</t>
+  </si>
+  <si>
+    <t>조세 제도 정비</t>
+  </si>
+  <si>
+    <t>politics</t>
+  </si>
+  <si>
+    <t>foreign_diplomacy</t>
+  </si>
+  <si>
+    <t>인근 제후국 외교</t>
+  </si>
+  <si>
+    <t>enemy_intelligence</t>
+  </si>
+  <si>
+    <t>적진 첩보 수집</t>
+  </si>
+  <si>
+    <t>intellect</t>
+  </si>
+  <si>
+    <t>tactics_research</t>
+  </si>
+  <si>
+    <t>병법서 연구</t>
+  </si>
+  <si>
+    <t>refugee_persuasion</t>
+  </si>
+  <si>
+    <t>유랑민 귀순 설득</t>
+  </si>
+  <si>
+    <t>charisma</t>
+  </si>
+  <si>
+    <t>recruit_talent</t>
+  </si>
+  <si>
+    <t>재야 인재 영입</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>unlock_pct</t>
+  </si>
+  <si>
+    <t>reward_key</t>
+  </si>
+  <si>
+    <t>reward_value</t>
+  </si>
+  <si>
+    <t>reward_min</t>
+  </si>
+  <si>
+    <t>reward_max</t>
+  </si>
+  <si>
+    <t>drop_rate</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>rice</t>
+  </si>
+  <si>
+    <t>bundle_elite</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>bundle_hero</t>
+  </si>
+  <si>
+    <t>treasure_piece</t>
+  </si>
+  <si>
+    <t>legend</t>
+  </si>
+  <si>
+    <t>treasure</t>
+  </si>
+  <si>
+    <t>leadership</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strength</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>intellect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>politics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>charisma</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>general</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>legend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,8 +377,21 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,8 +404,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFE2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -231,13 +434,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -248,6 +481,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -669,6 +914,86 @@
       </c>
       <c r="B7" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -956,4 +1281,2798 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8633AE6D-7B52-48DE-9717-BAAA3077CF3B}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="6">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76F873B-B31A-4110-93A3-D7A2ED5125F3}">
+  <dimension ref="A1:I92"/>
+  <sheetFormatPr defaultColWidth="36" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="6">
+        <f>VLOOKUP(B3,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="6">
+        <v>100</v>
+      </c>
+      <c r="H3" s="6">
+        <v>200</v>
+      </c>
+      <c r="I3" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="6">
+        <f>VLOOKUP(B4,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="6">
+        <v>50</v>
+      </c>
+      <c r="H4" s="6">
+        <v>100</v>
+      </c>
+      <c r="I4" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="6">
+        <f>VLOOKUP(B5,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="6">
+        <v>25</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="6">
+        <f>VLOOKUP(B6,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>50</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="6">
+        <f>VLOOKUP(B7,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>100</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="6">
+        <f>VLOOKUP(B8,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="6">
+        <v>500</v>
+      </c>
+      <c r="H8" s="6">
+        <v>800</v>
+      </c>
+      <c r="I8" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="6">
+        <f>VLOOKUP(B9,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="6">
+        <v>200</v>
+      </c>
+      <c r="H9" s="6">
+        <v>400</v>
+      </c>
+      <c r="I9" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="6">
+        <f>VLOOKUP(B10,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>25</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="6">
+        <f>VLOOKUP(B11,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>50</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="6">
+        <f>VLOOKUP(B12,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D12" s="6">
+        <v>75</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="6">
+        <f>VLOOKUP(B13,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D13" s="6">
+        <v>100</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="6">
+        <f>VLOOKUP(B14,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H14" s="6">
+        <v>3000</v>
+      </c>
+      <c r="I14" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="6">
+        <f>VLOOKUP(B15,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="7"/>
+      <c r="G15" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I15" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="6">
+        <f>VLOOKUP(B16,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="6">
+        <v>25</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="7"/>
+      <c r="G16" s="6">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6">
+        <v>3</v>
+      </c>
+      <c r="I16" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="6">
+        <f>VLOOKUP(B17,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D17" s="6">
+        <v>50</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="6">
+        <v>1</v>
+      </c>
+      <c r="H17" s="6">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="6">
+        <f>VLOOKUP(B18,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D18" s="6">
+        <v>75</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="6">
+        <f>VLOOKUP(B19,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="6">
+        <v>90</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="6">
+        <f>VLOOKUP(B20,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="6">
+        <v>100</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="6">
+        <v>1</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="6">
+        <f>VLOOKUP(B21,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="6">
+        <v>100</v>
+      </c>
+      <c r="H21" s="6">
+        <v>200</v>
+      </c>
+      <c r="I21" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="6">
+        <f>VLOOKUP(B22,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="6">
+        <v>50</v>
+      </c>
+      <c r="H22" s="6">
+        <v>100</v>
+      </c>
+      <c r="I22" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="6">
+        <f>VLOOKUP(B23,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="6">
+        <v>25</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="6">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="6">
+        <f>VLOOKUP(B24,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="6">
+        <v>50</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="6">
+        <v>1</v>
+      </c>
+      <c r="H24" s="6">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="6">
+        <f>VLOOKUP(B25,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="6">
+        <v>100</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1</v>
+      </c>
+      <c r="H25" s="6">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="6">
+        <f>VLOOKUP(B26,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="6">
+        <v>500</v>
+      </c>
+      <c r="H26" s="6">
+        <v>800</v>
+      </c>
+      <c r="I26" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="6">
+        <f>VLOOKUP(B27,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="6">
+        <v>200</v>
+      </c>
+      <c r="H27" s="6">
+        <v>400</v>
+      </c>
+      <c r="I27" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="6">
+        <f>VLOOKUP(B28,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D28" s="6">
+        <v>25</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="6">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6">
+        <v>2</v>
+      </c>
+      <c r="I28" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="6">
+        <f>VLOOKUP(B29,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D29" s="6">
+        <v>50</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="6">
+        <v>1</v>
+      </c>
+      <c r="H29" s="6">
+        <v>1</v>
+      </c>
+      <c r="I29" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="6">
+        <f>VLOOKUP(B30,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D30" s="6">
+        <v>75</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="6">
+        <v>1</v>
+      </c>
+      <c r="H30" s="6">
+        <v>1</v>
+      </c>
+      <c r="I30" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="6">
+        <f>VLOOKUP(B31,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D31" s="6">
+        <v>100</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="6">
+        <v>1</v>
+      </c>
+      <c r="H31" s="6">
+        <v>1</v>
+      </c>
+      <c r="I31" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="6">
+        <f>VLOOKUP(B32,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="7"/>
+      <c r="G32" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H32" s="6">
+        <v>3000</v>
+      </c>
+      <c r="I32" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="6">
+        <f>VLOOKUP(B33,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H33" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I33" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="6">
+        <f>VLOOKUP(B34,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D34" s="6">
+        <v>25</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="7"/>
+      <c r="G34" s="6">
+        <v>2</v>
+      </c>
+      <c r="H34" s="6">
+        <v>3</v>
+      </c>
+      <c r="I34" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="6">
+        <f>VLOOKUP(B35,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D35" s="6">
+        <v>50</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="7"/>
+      <c r="G35" s="6">
+        <v>1</v>
+      </c>
+      <c r="H35" s="6">
+        <v>1</v>
+      </c>
+      <c r="I35" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="6">
+        <f>VLOOKUP(B36,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D36" s="6">
+        <v>75</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" s="6">
+        <v>1</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1</v>
+      </c>
+      <c r="I36" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="6">
+        <f>VLOOKUP(B37,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D37" s="6">
+        <v>90</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="6">
+        <v>1</v>
+      </c>
+      <c r="H37" s="6">
+        <v>1</v>
+      </c>
+      <c r="I37" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="6">
+        <f>VLOOKUP(B38,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D38" s="6">
+        <v>100</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="6">
+        <v>1</v>
+      </c>
+      <c r="H38" s="6">
+        <v>1</v>
+      </c>
+      <c r="I38" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="6">
+        <f>VLOOKUP(B39,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="7"/>
+      <c r="G39" s="6">
+        <v>100</v>
+      </c>
+      <c r="H39" s="6">
+        <v>200</v>
+      </c>
+      <c r="I39" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="6">
+        <f>VLOOKUP(B40,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F40" s="7"/>
+      <c r="G40" s="6">
+        <v>50</v>
+      </c>
+      <c r="H40" s="6">
+        <v>100</v>
+      </c>
+      <c r="I40" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="6">
+        <f>VLOOKUP(B41,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="6">
+        <v>25</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="7"/>
+      <c r="G41" s="6">
+        <v>1</v>
+      </c>
+      <c r="H41" s="6">
+        <v>1</v>
+      </c>
+      <c r="I41" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="6">
+        <f>VLOOKUP(B42,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
+        <v>50</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="6">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6">
+        <v>1</v>
+      </c>
+      <c r="I42" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="6">
+        <f>VLOOKUP(B43,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="6">
+        <v>100</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G43" s="6">
+        <v>1</v>
+      </c>
+      <c r="H43" s="6">
+        <v>1</v>
+      </c>
+      <c r="I43" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" s="6">
+        <f>VLOOKUP(B44,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F44" s="7"/>
+      <c r="G44" s="6">
+        <v>500</v>
+      </c>
+      <c r="H44" s="6">
+        <v>800</v>
+      </c>
+      <c r="I44" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="6">
+        <f>VLOOKUP(B45,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" s="7"/>
+      <c r="G45" s="6">
+        <v>200</v>
+      </c>
+      <c r="H45" s="6">
+        <v>400</v>
+      </c>
+      <c r="I45" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="6">
+        <f>VLOOKUP(B46,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D46" s="6">
+        <v>25</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F46" s="7"/>
+      <c r="G46" s="6">
+        <v>1</v>
+      </c>
+      <c r="H46" s="6">
+        <v>2</v>
+      </c>
+      <c r="I46" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="6">
+        <f>VLOOKUP(B47,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>50</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F47" s="7"/>
+      <c r="G47" s="6">
+        <v>1</v>
+      </c>
+      <c r="H47" s="6">
+        <v>1</v>
+      </c>
+      <c r="I47" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="6">
+        <f>VLOOKUP(B48,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D48" s="6">
+        <v>75</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G48" s="6">
+        <v>1</v>
+      </c>
+      <c r="H48" s="6">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="6">
+        <f>VLOOKUP(B49,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D49" s="6">
+        <v>100</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49" s="7"/>
+      <c r="G49" s="6">
+        <v>1</v>
+      </c>
+      <c r="H49" s="6">
+        <v>1</v>
+      </c>
+      <c r="I49" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="6">
+        <f>VLOOKUP(B50,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" s="7"/>
+      <c r="G50" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H50" s="6">
+        <v>3000</v>
+      </c>
+      <c r="I50" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="6">
+        <f>VLOOKUP(B51,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" s="7"/>
+      <c r="G51" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H51" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I51" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C52" s="6">
+        <f>VLOOKUP(B52,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>25</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="7"/>
+      <c r="G52" s="6">
+        <v>2</v>
+      </c>
+      <c r="H52" s="6">
+        <v>3</v>
+      </c>
+      <c r="I52" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="6">
+        <f>VLOOKUP(B53,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D53" s="6">
+        <v>50</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="7"/>
+      <c r="G53" s="6">
+        <v>1</v>
+      </c>
+      <c r="H53" s="6">
+        <v>1</v>
+      </c>
+      <c r="I53" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C54" s="6">
+        <f>VLOOKUP(B54,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D54" s="6">
+        <v>75</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G54" s="6">
+        <v>1</v>
+      </c>
+      <c r="H54" s="6">
+        <v>1</v>
+      </c>
+      <c r="I54" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C55" s="6">
+        <f>VLOOKUP(B55,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D55" s="6">
+        <v>90</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" s="7"/>
+      <c r="G55" s="6">
+        <v>1</v>
+      </c>
+      <c r="H55" s="6">
+        <v>1</v>
+      </c>
+      <c r="I55" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C56" s="6">
+        <f>VLOOKUP(B56,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D56" s="6">
+        <v>100</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" s="7"/>
+      <c r="G56" s="6">
+        <v>1</v>
+      </c>
+      <c r="H56" s="6">
+        <v>1</v>
+      </c>
+      <c r="I56" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57" s="6">
+        <f>VLOOKUP(B57,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="6">
+        <v>0</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F57" s="7"/>
+      <c r="G57" s="6">
+        <v>100</v>
+      </c>
+      <c r="H57" s="6">
+        <v>200</v>
+      </c>
+      <c r="I57" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" s="6">
+        <f>VLOOKUP(B58,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F58" s="7"/>
+      <c r="G58" s="6">
+        <v>50</v>
+      </c>
+      <c r="H58" s="6">
+        <v>100</v>
+      </c>
+      <c r="I58" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" s="6">
+        <f>VLOOKUP(B59,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="6">
+        <v>25</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F59" s="7"/>
+      <c r="G59" s="6">
+        <v>1</v>
+      </c>
+      <c r="H59" s="6">
+        <v>1</v>
+      </c>
+      <c r="I59" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="6">
+        <f>VLOOKUP(B60,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="6">
+        <v>50</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F60" s="7"/>
+      <c r="G60" s="6">
+        <v>1</v>
+      </c>
+      <c r="H60" s="6">
+        <v>1</v>
+      </c>
+      <c r="I60" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="6">
+        <f>VLOOKUP(B61,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="6">
+        <v>100</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G61" s="6">
+        <v>1</v>
+      </c>
+      <c r="H61" s="6">
+        <v>1</v>
+      </c>
+      <c r="I61" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C62" s="6">
+        <f>VLOOKUP(B62,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D62" s="6">
+        <v>0</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F62" s="7"/>
+      <c r="G62" s="6">
+        <v>500</v>
+      </c>
+      <c r="H62" s="6">
+        <v>800</v>
+      </c>
+      <c r="I62" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" s="6">
+        <f>VLOOKUP(B63,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D63" s="6">
+        <v>0</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F63" s="7"/>
+      <c r="G63" s="6">
+        <v>200</v>
+      </c>
+      <c r="H63" s="6">
+        <v>400</v>
+      </c>
+      <c r="I63" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="6">
+        <f>VLOOKUP(B64,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D64" s="6">
+        <v>25</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F64" s="7"/>
+      <c r="G64" s="6">
+        <v>1</v>
+      </c>
+      <c r="H64" s="6">
+        <v>2</v>
+      </c>
+      <c r="I64" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="6">
+        <f>VLOOKUP(B65,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D65" s="6">
+        <v>50</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F65" s="7"/>
+      <c r="G65" s="6">
+        <v>1</v>
+      </c>
+      <c r="H65" s="6">
+        <v>1</v>
+      </c>
+      <c r="I65" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66" s="6">
+        <f>VLOOKUP(B66,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D66" s="6">
+        <v>75</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G66" s="6">
+        <v>1</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1</v>
+      </c>
+      <c r="I66" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="6">
+        <f>VLOOKUP(B67,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D67" s="6">
+        <v>100</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F67" s="7"/>
+      <c r="G67" s="6">
+        <v>1</v>
+      </c>
+      <c r="H67" s="6">
+        <v>1</v>
+      </c>
+      <c r="I67" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" s="6">
+        <f>VLOOKUP(B68,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D68" s="6">
+        <v>0</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F68" s="7"/>
+      <c r="G68" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H68" s="6">
+        <v>3000</v>
+      </c>
+      <c r="I68" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C69" s="6">
+        <f>VLOOKUP(B69,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F69" s="7"/>
+      <c r="G69" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H69" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I69" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" s="6">
+        <f>VLOOKUP(B70,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D70" s="6">
+        <v>25</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F70" s="7"/>
+      <c r="G70" s="6">
+        <v>2</v>
+      </c>
+      <c r="H70" s="6">
+        <v>3</v>
+      </c>
+      <c r="I70" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" s="6">
+        <f>VLOOKUP(B71,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D71" s="6">
+        <v>50</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F71" s="7"/>
+      <c r="G71" s="6">
+        <v>1</v>
+      </c>
+      <c r="H71" s="6">
+        <v>1</v>
+      </c>
+      <c r="I71" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" s="6">
+        <f>VLOOKUP(B72,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D72" s="6">
+        <v>75</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G72" s="6">
+        <v>1</v>
+      </c>
+      <c r="H72" s="6">
+        <v>1</v>
+      </c>
+      <c r="I72" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73" s="6">
+        <f>VLOOKUP(B73,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D73" s="6">
+        <v>90</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F73" s="7"/>
+      <c r="G73" s="6">
+        <v>1</v>
+      </c>
+      <c r="H73" s="6">
+        <v>1</v>
+      </c>
+      <c r="I73" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" s="6">
+        <f>VLOOKUP(B74,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D74" s="6">
+        <v>100</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F74" s="7"/>
+      <c r="G74" s="6">
+        <v>1</v>
+      </c>
+      <c r="H74" s="6">
+        <v>1</v>
+      </c>
+      <c r="I74" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" s="6">
+        <f>VLOOKUP(B75,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D75" s="6">
+        <v>0</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F75" s="7"/>
+      <c r="G75" s="6">
+        <v>100</v>
+      </c>
+      <c r="H75" s="6">
+        <v>200</v>
+      </c>
+      <c r="I75" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C76" s="6">
+        <f>VLOOKUP(B76,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D76" s="6">
+        <v>0</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F76" s="7"/>
+      <c r="G76" s="6">
+        <v>50</v>
+      </c>
+      <c r="H76" s="6">
+        <v>100</v>
+      </c>
+      <c r="I76" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="6">
+        <f>VLOOKUP(B77,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D77" s="6">
+        <v>25</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F77" s="7"/>
+      <c r="G77" s="6">
+        <v>1</v>
+      </c>
+      <c r="H77" s="6">
+        <v>1</v>
+      </c>
+      <c r="I77" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" s="6">
+        <f>VLOOKUP(B78,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D78" s="6">
+        <v>50</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F78" s="7"/>
+      <c r="G78" s="6">
+        <v>1</v>
+      </c>
+      <c r="H78" s="6">
+        <v>1</v>
+      </c>
+      <c r="I78" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="6">
+        <f>VLOOKUP(B79,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="6">
+        <v>100</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G79" s="6">
+        <v>1</v>
+      </c>
+      <c r="H79" s="6">
+        <v>1</v>
+      </c>
+      <c r="I79" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C80" s="6">
+        <f>VLOOKUP(B80,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D80" s="6">
+        <v>0</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F80" s="7"/>
+      <c r="G80" s="6">
+        <v>500</v>
+      </c>
+      <c r="H80" s="6">
+        <v>800</v>
+      </c>
+      <c r="I80" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C81" s="6">
+        <f>VLOOKUP(B81,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D81" s="6">
+        <v>0</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F81" s="7"/>
+      <c r="G81" s="6">
+        <v>200</v>
+      </c>
+      <c r="H81" s="6">
+        <v>400</v>
+      </c>
+      <c r="I81" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" s="6">
+        <f>VLOOKUP(B82,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D82" s="6">
+        <v>25</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F82" s="7"/>
+      <c r="G82" s="6">
+        <v>1</v>
+      </c>
+      <c r="H82" s="6">
+        <v>2</v>
+      </c>
+      <c r="I82" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C83" s="6">
+        <f>VLOOKUP(B83,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D83" s="6">
+        <v>50</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F83" s="7"/>
+      <c r="G83" s="6">
+        <v>1</v>
+      </c>
+      <c r="H83" s="6">
+        <v>1</v>
+      </c>
+      <c r="I83" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C84" s="6">
+        <f>VLOOKUP(B84,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D84" s="6">
+        <v>75</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84" s="6">
+        <v>1</v>
+      </c>
+      <c r="H84" s="6">
+        <v>1</v>
+      </c>
+      <c r="I84" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C85" s="6">
+        <f>VLOOKUP(B85,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="D85" s="6">
+        <v>100</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F85" s="7"/>
+      <c r="G85" s="6">
+        <v>1</v>
+      </c>
+      <c r="H85" s="6">
+        <v>1</v>
+      </c>
+      <c r="I85" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C86" s="6">
+        <f>VLOOKUP(B86,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D86" s="6">
+        <v>0</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F86" s="7"/>
+      <c r="G86" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H86" s="6">
+        <v>3000</v>
+      </c>
+      <c r="I86" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C87" s="6">
+        <f>VLOOKUP(B87,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D87" s="6">
+        <v>0</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F87" s="7"/>
+      <c r="G87" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H87" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I87" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C88" s="6">
+        <f>VLOOKUP(B88,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D88" s="6">
+        <v>25</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F88" s="7"/>
+      <c r="G88" s="6">
+        <v>2</v>
+      </c>
+      <c r="H88" s="6">
+        <v>3</v>
+      </c>
+      <c r="I88" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89" s="6">
+        <f>VLOOKUP(B89,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D89" s="6">
+        <v>50</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F89" s="7"/>
+      <c r="G89" s="6">
+        <v>1</v>
+      </c>
+      <c r="H89" s="6">
+        <v>1</v>
+      </c>
+      <c r="I89" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C90" s="6">
+        <f>VLOOKUP(B90,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D90" s="6">
+        <v>75</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G90" s="6">
+        <v>1</v>
+      </c>
+      <c r="H90" s="6">
+        <v>1</v>
+      </c>
+      <c r="I90" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C91" s="6">
+        <f>VLOOKUP(B91,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D91" s="6">
+        <v>90</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F91" s="7"/>
+      <c r="G91" s="6">
+        <v>1</v>
+      </c>
+      <c r="H91" s="6">
+        <v>1</v>
+      </c>
+      <c r="I91" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C92" s="6">
+        <f>VLOOKUP(B92,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D92" s="6">
+        <v>100</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F92" s="7"/>
+      <c r="G92" s="6">
+        <v>1</v>
+      </c>
+      <c r="H92" s="6">
+        <v>1</v>
+      </c>
+      <c r="I92" s="6">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ExcelToJSONConverter/excel/castle.xlsx
+++ b/ExcelToJSONConverter/excel/castle.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F8AA5FF-A301-478E-93AF-1E24F4C2AC1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA05678F-0320-426B-ABB5-E6B303E23DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="94">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -345,6 +345,10 @@
   </si>
   <si>
     <t>#grade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1451,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76F873B-B31A-4110-93A3-D7A2ED5125F3}">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultColWidth="36" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
@@ -1617,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="6">
@@ -1645,14 +1649,12 @@
         <v>0</v>
       </c>
       <c r="D7" s="6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F7" s="7"/>
       <c r="G7" s="6">
         <v>1</v>
       </c>
@@ -1660,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1668,27 +1670,27 @@
         <v>43</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C8" s="6">
         <f>VLOOKUP(B8,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="6">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6">
-        <v>800</v>
+        <v>1</v>
       </c>
       <c r="I8" s="6">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1696,27 +1698,29 @@
         <v>43</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C9" s="6">
         <f>VLOOKUP(B9,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G9" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H9" s="6">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="I9" s="6">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1731,20 +1735,20 @@
         <v>2</v>
       </c>
       <c r="D10" s="6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="6">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H10" s="6">
-        <v>2</v>
+        <v>800</v>
       </c>
       <c r="I10" s="6">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1759,20 +1763,20 @@
         <v>2</v>
       </c>
       <c r="D11" s="6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H11" s="6">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="I11" s="6">
-        <v>35</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1787,22 +1791,20 @@
         <v>2</v>
       </c>
       <c r="D12" s="6">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F12" s="7"/>
       <c r="G12" s="6">
         <v>1</v>
       </c>
       <c r="H12" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="6">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1817,10 +1819,10 @@
         <v>2</v>
       </c>
       <c r="D13" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="6">
@@ -1830,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="6">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1838,27 +1840,27 @@
         <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C14" s="6">
         <f>VLOOKUP(B14,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="6">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6">
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="I14" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1866,27 +1868,27 @@
         <v>43</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C15" s="6">
         <f>VLOOKUP(B15,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="7"/>
+        <v>93</v>
+      </c>
+      <c r="F15" s="6"/>
       <c r="G15" s="6">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I15" s="6">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1894,27 +1896,29 @@
         <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C16" s="6">
         <f>VLOOKUP(B16,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G16" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1922,17 +1926,17 @@
         <v>43</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C17" s="6">
         <f>VLOOKUP(B17,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D17" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="6">
@@ -1942,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1957,22 +1961,20 @@
         <v>4</v>
       </c>
       <c r="D18" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F18" s="7"/>
       <c r="G18" s="6">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="H18" s="6">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="I18" s="6">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1987,20 +1989,20 @@
         <v>4</v>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H19" s="6">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I19" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2015,94 +2017,96 @@
         <v>4</v>
       </c>
       <c r="D20" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="6">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C21" s="6">
         <f>VLOOKUP(B21,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C22" s="6">
         <f>VLOOKUP(B22,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G22" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H22" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I22" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C23" s="6">
         <f>VLOOKUP(B23,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="6">
@@ -2112,25 +2116,25 @@
         <v>1</v>
       </c>
       <c r="I23" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C24" s="6">
         <f>VLOOKUP(B24,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D24" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="6">
@@ -2140,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2155,22 +2159,20 @@
         <v>0</v>
       </c>
       <c r="D25" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F25" s="7"/>
       <c r="G25" s="6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H25" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I25" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2178,11 +2180,11 @@
         <v>48</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C26" s="6">
         <f>VLOOKUP(B26,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" s="6">
         <v>0</v>
@@ -2192,10 +2194,10 @@
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="6">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H26" s="6">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="I26" s="6">
         <v>100</v>
@@ -2206,27 +2208,27 @@
         <v>48</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C27" s="6">
         <f>VLOOKUP(B27,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="I27" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2234,14 +2236,14 @@
         <v>48</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C28" s="6">
         <f>VLOOKUP(B28,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D28" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>75</v>
@@ -2251,10 +2253,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2262,19 +2264,21 @@
         <v>48</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C29" s="6">
         <f>VLOOKUP(B29,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G29" s="6">
         <v>1</v>
       </c>
@@ -2282,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2297,22 +2301,20 @@
         <v>2</v>
       </c>
       <c r="D30" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F30" s="7"/>
       <c r="G30" s="6">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H30" s="6">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="I30" s="6">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2327,20 +2329,20 @@
         <v>2</v>
       </c>
       <c r="D31" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F31" s="7"/>
       <c r="G31" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H31" s="6">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="I31" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2348,27 +2350,27 @@
         <v>48</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C32" s="6">
         <f>VLOOKUP(B32,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D32" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" s="6">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="H32" s="6">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="I32" s="6">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2376,27 +2378,27 @@
         <v>48</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C33" s="6">
         <f>VLOOKUP(B33,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="6">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H33" s="6">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I33" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2404,27 +2406,29 @@
         <v>48</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C34" s="6">
         <f>VLOOKUP(B34,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D34" s="6">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G34" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I34" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2432,17 +2436,17 @@
         <v>48</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C35" s="6">
         <f>VLOOKUP(B35,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="6">
@@ -2452,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2467,22 +2471,20 @@
         <v>4</v>
       </c>
       <c r="D36" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F36" s="7"/>
       <c r="G36" s="6">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="H36" s="6">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="I36" s="6">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2497,20 +2499,20 @@
         <v>4</v>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H37" s="6">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I37" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2525,94 +2527,96 @@
         <v>4</v>
       </c>
       <c r="D38" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" s="6">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C39" s="6">
         <f>VLOOKUP(B39,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="I39" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C40" s="6">
         <f>VLOOKUP(B40,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D40" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F40" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G40" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I40" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C41" s="6">
         <f>VLOOKUP(B41,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D41" s="6">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="6">
@@ -2622,25 +2626,25 @@
         <v>1</v>
       </c>
       <c r="I41" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C42" s="6">
         <f>VLOOKUP(B42,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D42" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="6">
@@ -2650,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2665,22 +2669,20 @@
         <v>0</v>
       </c>
       <c r="D43" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F43" s="7"/>
       <c r="G43" s="6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H43" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I43" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2688,11 +2690,11 @@
         <v>58</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C44" s="6">
         <f>VLOOKUP(B44,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44" s="6">
         <v>0</v>
@@ -2702,10 +2704,10 @@
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="6">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H44" s="6">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="I44" s="6">
         <v>100</v>
@@ -2716,27 +2718,27 @@
         <v>58</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C45" s="6">
         <f>VLOOKUP(B45,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H45" s="6">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2744,14 +2746,14 @@
         <v>58</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C46" s="6">
         <f>VLOOKUP(B46,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D46" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>75</v>
@@ -2761,10 +2763,10 @@
         <v>1</v>
       </c>
       <c r="H46" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2772,19 +2774,21 @@
         <v>58</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C47" s="6">
         <f>VLOOKUP(B47,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F47" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G47" s="6">
         <v>1</v>
       </c>
@@ -2792,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2807,22 +2811,20 @@
         <v>2</v>
       </c>
       <c r="D48" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F48" s="7"/>
       <c r="G48" s="6">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H48" s="6">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="I48" s="6">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2837,20 +2839,20 @@
         <v>2</v>
       </c>
       <c r="D49" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H49" s="6">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="I49" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2858,27 +2860,27 @@
         <v>58</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C50" s="6">
         <f>VLOOKUP(B50,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="6">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="H50" s="6">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="I50" s="6">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2886,27 +2888,27 @@
         <v>58</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C51" s="6">
         <f>VLOOKUP(B51,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D51" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="6">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H51" s="6">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I51" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2914,27 +2916,29 @@
         <v>58</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C52" s="6">
         <f>VLOOKUP(B52,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D52" s="6">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F52" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G52" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2942,17 +2946,17 @@
         <v>58</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C53" s="6">
         <f>VLOOKUP(B53,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="6">
@@ -2962,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2977,22 +2981,20 @@
         <v>4</v>
       </c>
       <c r="D54" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F54" s="7"/>
       <c r="G54" s="6">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="H54" s="6">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="I54" s="6">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3007,20 +3009,20 @@
         <v>4</v>
       </c>
       <c r="D55" s="6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H55" s="6">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I55" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3035,94 +3037,96 @@
         <v>4</v>
       </c>
       <c r="D56" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" s="6">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C57" s="6">
         <f>VLOOKUP(B57,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D57" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H57" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="I57" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C58" s="6">
         <f>VLOOKUP(B58,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D58" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F58" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G58" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H58" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I58" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C59" s="6">
         <f>VLOOKUP(B59,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D59" s="6">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="6">
@@ -3132,25 +3136,25 @@
         <v>1</v>
       </c>
       <c r="I59" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C60" s="6">
         <f>VLOOKUP(B60,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D60" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="6">
@@ -3160,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3175,22 +3179,20 @@
         <v>0</v>
       </c>
       <c r="D61" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F61" s="7"/>
       <c r="G61" s="6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H61" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I61" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3198,11 +3200,11 @@
         <v>53</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C62" s="6">
         <f>VLOOKUP(B62,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62" s="6">
         <v>0</v>
@@ -3212,10 +3214,10 @@
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="6">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H62" s="6">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="I62" s="6">
         <v>100</v>
@@ -3226,27 +3228,27 @@
         <v>53</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C63" s="6">
         <f>VLOOKUP(B63,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H63" s="6">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="I63" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3254,14 +3256,14 @@
         <v>53</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C64" s="6">
         <f>VLOOKUP(B64,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>75</v>
@@ -3271,10 +3273,10 @@
         <v>1</v>
       </c>
       <c r="H64" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3282,19 +3284,21 @@
         <v>53</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C65" s="6">
         <f>VLOOKUP(B65,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D65" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F65" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G65" s="6">
         <v>1</v>
       </c>
@@ -3302,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3317,22 +3321,20 @@
         <v>2</v>
       </c>
       <c r="D66" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F66" s="7"/>
       <c r="G66" s="6">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H66" s="6">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="I66" s="6">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3347,20 +3349,20 @@
         <v>2</v>
       </c>
       <c r="D67" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H67" s="6">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="I67" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3368,27 +3370,27 @@
         <v>53</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C68" s="6">
         <f>VLOOKUP(B68,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D68" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="6">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="H68" s="6">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="I68" s="6">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3396,27 +3398,27 @@
         <v>53</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C69" s="6">
         <f>VLOOKUP(B69,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="6">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H69" s="6">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I69" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3424,27 +3426,29 @@
         <v>53</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C70" s="6">
         <f>VLOOKUP(B70,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70" s="6">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F70" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G70" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I70" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3452,17 +3456,17 @@
         <v>53</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C71" s="6">
         <f>VLOOKUP(B71,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D71" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="6">
@@ -3472,7 +3476,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3487,22 +3491,20 @@
         <v>4</v>
       </c>
       <c r="D72" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F72" s="7"/>
       <c r="G72" s="6">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="H72" s="6">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="I72" s="6">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3517,20 +3519,20 @@
         <v>4</v>
       </c>
       <c r="D73" s="6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H73" s="6">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I73" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3545,94 +3547,96 @@
         <v>4</v>
       </c>
       <c r="D74" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I74" s="6">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C75" s="6">
         <f>VLOOKUP(B75,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D75" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H75" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="I75" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C76" s="6">
         <f>VLOOKUP(B76,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D76" s="6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F76" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G76" s="6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I76" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C77" s="6">
         <f>VLOOKUP(B77,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D77" s="6">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="6">
@@ -3642,25 +3646,25 @@
         <v>1</v>
       </c>
       <c r="I77" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C78" s="6">
         <f>VLOOKUP(B78,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D78" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="6">
@@ -3670,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="I78" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3685,22 +3689,20 @@
         <v>0</v>
       </c>
       <c r="D79" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F79" s="7"/>
       <c r="G79" s="6">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H79" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="I79" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3708,11 +3710,11 @@
         <v>63</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C80" s="6">
         <f>VLOOKUP(B80,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80" s="6">
         <v>0</v>
@@ -3722,10 +3724,10 @@
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="6">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="H80" s="6">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="I80" s="6">
         <v>100</v>
@@ -3736,27 +3738,27 @@
         <v>63</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C81" s="6">
         <f>VLOOKUP(B81,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D81" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="6">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H81" s="6">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="I81" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3764,14 +3766,14 @@
         <v>63</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C82" s="6">
         <f>VLOOKUP(B82,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D82" s="6">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>75</v>
@@ -3781,10 +3783,10 @@
         <v>1</v>
       </c>
       <c r="H82" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I82" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3792,19 +3794,21 @@
         <v>63</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C83" s="6">
         <f>VLOOKUP(B83,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F83" s="7"/>
+        <v>76</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G83" s="6">
         <v>1</v>
       </c>
@@ -3812,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3827,22 +3831,20 @@
         <v>2</v>
       </c>
       <c r="D84" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F84" s="7"/>
       <c r="G84" s="6">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="H84" s="6">
-        <v>1</v>
+        <v>800</v>
       </c>
       <c r="I84" s="6">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3857,20 +3859,20 @@
         <v>2</v>
       </c>
       <c r="D85" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F85" s="7"/>
       <c r="G85" s="6">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H85" s="6">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="I85" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3878,27 +3880,27 @@
         <v>63</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C86" s="6">
         <f>VLOOKUP(B86,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D86" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F86" s="7"/>
       <c r="G86" s="6">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="H86" s="6">
-        <v>3000</v>
+        <v>2</v>
       </c>
       <c r="I86" s="6">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3906,27 +3908,27 @@
         <v>63</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C87" s="6">
         <f>VLOOKUP(B87,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D87" s="6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>75</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="6">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6">
-        <v>1500</v>
+        <v>1</v>
       </c>
       <c r="I87" s="6">
-        <v>100</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3934,27 +3936,29 @@
         <v>63</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C88" s="6">
         <f>VLOOKUP(B88,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D88" s="6">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F88" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="G88" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I88" s="6">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3962,17 +3966,17 @@
         <v>63</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C89" s="6">
         <f>VLOOKUP(B89,Overview!$A$16:$B$20,2,FALSE)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D89" s="6">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="6">
@@ -3982,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3997,22 +4001,20 @@
         <v>4</v>
       </c>
       <c r="D90" s="6">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F90" s="7"/>
       <c r="G90" s="6">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="H90" s="6">
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="I90" s="6">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4027,20 +4029,20 @@
         <v>4</v>
       </c>
       <c r="D91" s="6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="6">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="H91" s="6">
-        <v>1</v>
+        <v>1500</v>
       </c>
       <c r="I91" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4055,24 +4057,139 @@
         <v>4</v>
       </c>
       <c r="D92" s="6">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F92" s="7"/>
       <c r="G92" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I92" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C93" s="6">
+        <f>VLOOKUP(B93,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D93" s="6">
+        <v>50</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F93" s="7"/>
+      <c r="G93" s="6">
+        <v>1</v>
+      </c>
+      <c r="H93" s="6">
+        <v>1</v>
+      </c>
+      <c r="I93" s="6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C94" s="6">
+        <f>VLOOKUP(B94,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D94" s="6">
+        <v>75</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G94" s="6">
+        <v>1</v>
+      </c>
+      <c r="H94" s="6">
+        <v>1</v>
+      </c>
+      <c r="I94" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C95" s="6">
+        <f>VLOOKUP(B95,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D95" s="6">
+        <v>90</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F95" s="7"/>
+      <c r="G95" s="6">
+        <v>1</v>
+      </c>
+      <c r="H95" s="6">
+        <v>1</v>
+      </c>
+      <c r="I95" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C96" s="6">
+        <f>VLOOKUP(B96,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="D96" s="6">
+        <v>100</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F96" s="7"/>
+      <c r="G96" s="6">
+        <v>1</v>
+      </c>
+      <c r="H96" s="6">
+        <v>1</v>
+      </c>
+      <c r="I96" s="6">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelToJSONConverter/excel/castle.xlsx
+++ b/ExcelToJSONConverter/excel/castle.xlsx
@@ -3,16 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA05678F-0320-426B-ABB5-E6B303E23DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25158BB-2BBF-4668-8A4B-B3066C87B63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Castle" sheetId="4" r:id="rId2"/>
     <sheet name="CastleRise" sheetId="3" r:id="rId3"/>
     <sheet name="CastleMission" sheetId="5" r:id="rId4"/>
-    <sheet name="CastleMissionReward" sheetId="6" r:id="rId5"/>
+    <sheet name="CastleMissionGrade" sheetId="8" r:id="rId5"/>
+    <sheet name="CastleMissionReward" sheetId="6" r:id="rId6"/>
+    <sheet name="CastleOfficeLevel" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="114">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -350,6 +352,68 @@
   <si>
     <t>gold</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>time_stone</t>
+  </si>
+  <si>
+    <t>bundle_normal</t>
+  </si>
+  <si>
+    <t>bundle_general</t>
+  </si>
+  <si>
+    <t>bundle_legend</t>
+  </si>
+  <si>
+    <t>public_soul_stone</t>
+  </si>
+  <si>
+    <t>class_soul_stone</t>
+  </si>
+  <si>
+    <t>dedicated_soul_stone</t>
+  </si>
+  <si>
+    <t>class_soul_stone_random_box</t>
+  </si>
+  <si>
+    <t>dedicated_soul_stone_random_box</t>
+  </si>
+  <si>
+    <t>treasure_piece_random_box</t>
+  </si>
+  <si>
+    <t>#reward_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration_seconds</t>
+  </si>
+  <si>
+    <t>mission_xp</t>
+  </si>
+  <si>
+    <t>req_stat_value</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>req_xp</t>
+  </si>
+  <si>
+    <t>accum_xp</t>
+  </si>
+  <si>
+    <t>upgrade_seconds</t>
   </si>
 </sst>
 </file>
@@ -474,7 +538,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -498,6 +562,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,10 +913,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="33" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -848,7 +927,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -862,7 +941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -876,7 +955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -890,7 +969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -904,7 +983,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -912,7 +991,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -920,84 +999,207 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>83</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10">
+        <f>G9+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>84</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11">
+        <f t="shared" ref="G11:G24" si="0">G10+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>85</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>86</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>87</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>91</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>90</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>89</v>
       </c>
       <c r="B20">
         <v>4</v>
+      </c>
+      <c r="F20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1454,22 +1656,130 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C384F46F-68D3-4E63-B700-B9F81B9C8277}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="10">
+        <f>VLOOKUP(A3,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="10">
+        <v>3600</v>
+      </c>
+      <c r="D3" s="10">
+        <v>10</v>
+      </c>
+      <c r="E3" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="10">
+        <f>VLOOKUP(A4,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="C4" s="10">
+        <v>21600</v>
+      </c>
+      <c r="D4" s="10">
+        <v>60</v>
+      </c>
+      <c r="E4" s="10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="10">
+        <f>VLOOKUP(A5,Overview!$A$16:$B$20,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="C5" s="10">
+        <v>86400</v>
+      </c>
+      <c r="D5" s="10">
+        <v>240</v>
+      </c>
+      <c r="E5" s="10">
+        <v>500</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76F873B-B31A-4110-93A3-D7A2ED5125F3}">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr defaultColWidth="36" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="1" max="1" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
@@ -1483,22 +1793,25 @@
         <v>67</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1513,19 +1826,22 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>82</v>
       </c>
@@ -1542,18 +1858,22 @@
       <c r="E3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="6">
-        <v>100</v>
-      </c>
+      <c r="F3" s="6">
+        <f>VLOOKUP(E3,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="7"/>
       <c r="H3" s="6">
+        <v>100</v>
+      </c>
+      <c r="I3" s="6">
         <v>200</v>
       </c>
-      <c r="I3" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J3" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>43</v>
       </c>
@@ -1570,18 +1890,22 @@
       <c r="E4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="6">
+      <c r="F4" s="6">
+        <f>VLOOKUP(E4,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="6">
         <v>50</v>
       </c>
-      <c r="H4" s="6">
-        <v>100</v>
-      </c>
       <c r="I4" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J4" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>43</v>
       </c>
@@ -1598,18 +1922,22 @@
       <c r="E5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="6">
-        <v>1</v>
-      </c>
+      <c r="F5" s="6">
+        <f>VLOOKUP(E5,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G5" s="7"/>
       <c r="H5" s="6">
         <v>1</v>
       </c>
       <c r="I5" s="6">
+        <v>1</v>
+      </c>
+      <c r="J5" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>43</v>
       </c>
@@ -1626,18 +1954,22 @@
       <c r="E6" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
+      <c r="F6" s="6">
+        <f>VLOOKUP(E6,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="G6" s="7"/>
       <c r="H6" s="6">
         <v>1</v>
       </c>
       <c r="I6" s="6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
@@ -1654,18 +1986,22 @@
       <c r="E7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="6">
-        <v>1</v>
-      </c>
+      <c r="F7" s="6">
+        <f>VLOOKUP(E7,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G7" s="7"/>
       <c r="H7" s="6">
         <v>1</v>
       </c>
       <c r="I7" s="6">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1682,18 +2018,22 @@
       <c r="E8" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="6">
-        <v>1</v>
-      </c>
+      <c r="F8" s="6">
+        <f>VLOOKUP(E8,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="G8" s="7"/>
       <c r="H8" s="6">
         <v>1</v>
       </c>
       <c r="I8" s="6">
+        <v>1</v>
+      </c>
+      <c r="J8" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>43</v>
       </c>
@@ -1710,20 +2050,24 @@
       <c r="E9" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="6">
-        <v>1</v>
+      <c r="F9" s="6">
+        <f>VLOOKUP(E9,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H9" s="6">
         <v>1</v>
       </c>
       <c r="I9" s="6">
+        <v>1</v>
+      </c>
+      <c r="J9" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>43</v>
       </c>
@@ -1740,18 +2084,22 @@
       <c r="E10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="6">
+      <c r="F10" s="6">
+        <f>VLOOKUP(E10,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="6">
         <v>500</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>800</v>
       </c>
-      <c r="I10" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J10" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>43</v>
       </c>
@@ -1768,18 +2116,22 @@
       <c r="E11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="6">
+      <c r="F11" s="6">
+        <f>VLOOKUP(E11,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="6">
         <v>200</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>400</v>
       </c>
-      <c r="I11" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J11" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>43</v>
       </c>
@@ -1796,18 +2148,22 @@
       <c r="E12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="6">
-        <v>1</v>
-      </c>
+      <c r="F12" s="6">
+        <f>VLOOKUP(E12,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G12" s="7"/>
       <c r="H12" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" s="6">
+        <v>2</v>
+      </c>
+      <c r="J12" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>43</v>
       </c>
@@ -1824,18 +2180,22 @@
       <c r="E13" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="6">
-        <v>1</v>
-      </c>
+      <c r="F13" s="6">
+        <f>VLOOKUP(E13,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="G13" s="7"/>
       <c r="H13" s="6">
         <v>1</v>
       </c>
       <c r="I13" s="6">
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>43</v>
       </c>
@@ -1852,18 +2212,22 @@
       <c r="E14" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="6">
-        <v>1</v>
-      </c>
+      <c r="F14" s="6">
+        <f>VLOOKUP(E14,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G14" s="7"/>
       <c r="H14" s="6">
         <v>1</v>
       </c>
       <c r="I14" s="6">
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
@@ -1880,18 +2244,22 @@
       <c r="E15" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6">
-        <v>1</v>
-      </c>
+      <c r="F15" s="6">
+        <f>VLOOKUP(E15,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="G15" s="6"/>
       <c r="H15" s="6">
         <v>1</v>
       </c>
       <c r="I15" s="6">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>43</v>
       </c>
@@ -1908,20 +2276,24 @@
       <c r="E16" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="6">
-        <v>1</v>
+      <c r="F16" s="6">
+        <f>VLOOKUP(E16,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H16" s="6">
         <v>1</v>
       </c>
       <c r="I16" s="6">
+        <v>1</v>
+      </c>
+      <c r="J16" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
@@ -1938,18 +2310,22 @@
       <c r="E17" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="6">
-        <v>1</v>
-      </c>
+      <c r="F17" s="6">
+        <f>VLOOKUP(E17,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G17" s="7"/>
       <c r="H17" s="6">
         <v>1</v>
       </c>
       <c r="I17" s="6">
+        <v>1</v>
+      </c>
+      <c r="J17" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>43</v>
       </c>
@@ -1966,18 +2342,22 @@
       <c r="E18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="6">
+      <c r="F18" s="6">
+        <f>VLOOKUP(E18,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G18" s="7"/>
+      <c r="H18" s="6">
         <v>2000</v>
       </c>
-      <c r="H18" s="6">
+      <c r="I18" s="6">
         <v>3000</v>
       </c>
-      <c r="I18" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J18" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>43</v>
       </c>
@@ -1994,18 +2374,22 @@
       <c r="E19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="6">
+      <c r="F19" s="6">
+        <f>VLOOKUP(E19,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G19" s="7"/>
+      <c r="H19" s="6">
         <v>1000</v>
       </c>
-      <c r="H19" s="6">
+      <c r="I19" s="6">
         <v>1500</v>
       </c>
-      <c r="I19" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J19" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>43</v>
       </c>
@@ -2022,18 +2406,22 @@
       <c r="E20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="6">
-        <v>2</v>
-      </c>
+      <c r="F20" s="6">
+        <f>VLOOKUP(E20,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G20" s="7"/>
       <c r="H20" s="6">
+        <v>2</v>
+      </c>
+      <c r="I20" s="6">
         <v>3</v>
       </c>
-      <c r="I20" s="6">
+      <c r="J20" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
@@ -2050,18 +2438,22 @@
       <c r="E21" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="6">
-        <v>1</v>
-      </c>
+      <c r="F21" s="6">
+        <f>VLOOKUP(E21,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G21" s="7"/>
       <c r="H21" s="6">
         <v>1</v>
       </c>
       <c r="I21" s="6">
+        <v>1</v>
+      </c>
+      <c r="J21" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
@@ -2078,20 +2470,24 @@
       <c r="E22" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G22" s="6">
-        <v>1</v>
+      <c r="F22" s="6">
+        <f>VLOOKUP(E22,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H22" s="6">
         <v>1</v>
       </c>
       <c r="I22" s="6">
+        <v>1</v>
+      </c>
+      <c r="J22" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
@@ -2108,18 +2504,22 @@
       <c r="E23" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="6">
-        <v>1</v>
-      </c>
+      <c r="F23" s="6">
+        <f>VLOOKUP(E23,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G23" s="7"/>
       <c r="H23" s="6">
         <v>1</v>
       </c>
       <c r="I23" s="6">
+        <v>1</v>
+      </c>
+      <c r="J23" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>43</v>
       </c>
@@ -2136,18 +2536,22 @@
       <c r="E24" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="6">
-        <v>1</v>
-      </c>
+      <c r="F24" s="6">
+        <f>VLOOKUP(E24,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="G24" s="7"/>
       <c r="H24" s="6">
         <v>1</v>
       </c>
       <c r="I24" s="6">
+        <v>1</v>
+      </c>
+      <c r="J24" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>48</v>
       </c>
@@ -2164,18 +2568,22 @@
       <c r="E25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="6">
-        <v>100</v>
-      </c>
+      <c r="F25" s="6">
+        <f>VLOOKUP(E25,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G25" s="7"/>
       <c r="H25" s="6">
+        <v>100</v>
+      </c>
+      <c r="I25" s="6">
         <v>200</v>
       </c>
-      <c r="I25" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J25" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>48</v>
       </c>
@@ -2192,18 +2600,22 @@
       <c r="E26" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="6">
+      <c r="F26" s="6">
+        <f>VLOOKUP(E26,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G26" s="7"/>
+      <c r="H26" s="6">
         <v>50</v>
       </c>
-      <c r="H26" s="6">
-        <v>100</v>
-      </c>
       <c r="I26" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J26" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>48</v>
       </c>
@@ -2220,18 +2632,22 @@
       <c r="E27" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="6">
-        <v>1</v>
-      </c>
+      <c r="F27" s="6">
+        <f>VLOOKUP(E27,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G27" s="7"/>
       <c r="H27" s="6">
         <v>1</v>
       </c>
       <c r="I27" s="6">
+        <v>1</v>
+      </c>
+      <c r="J27" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>48</v>
       </c>
@@ -2248,18 +2664,22 @@
       <c r="E28" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="6">
-        <v>1</v>
-      </c>
+      <c r="F28" s="6">
+        <f>VLOOKUP(E28,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G28" s="7"/>
       <c r="H28" s="6">
         <v>1</v>
       </c>
       <c r="I28" s="6">
+        <v>1</v>
+      </c>
+      <c r="J28" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>48</v>
       </c>
@@ -2276,20 +2696,24 @@
       <c r="E29" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="6">
-        <v>1</v>
+      <c r="F29" s="6">
+        <f>VLOOKUP(E29,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H29" s="6">
         <v>1</v>
       </c>
       <c r="I29" s="6">
+        <v>1</v>
+      </c>
+      <c r="J29" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>48</v>
       </c>
@@ -2306,18 +2730,22 @@
       <c r="E30" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="6">
+      <c r="F30" s="6">
+        <f>VLOOKUP(E30,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G30" s="7"/>
+      <c r="H30" s="6">
         <v>500</v>
       </c>
-      <c r="H30" s="6">
+      <c r="I30" s="6">
         <v>800</v>
       </c>
-      <c r="I30" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J30" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>48</v>
       </c>
@@ -2334,18 +2762,22 @@
       <c r="E31" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="7"/>
-      <c r="G31" s="6">
+      <c r="F31" s="6">
+        <f>VLOOKUP(E31,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G31" s="7"/>
+      <c r="H31" s="6">
         <v>200</v>
       </c>
-      <c r="H31" s="6">
+      <c r="I31" s="6">
         <v>400</v>
       </c>
-      <c r="I31" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J31" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>48</v>
       </c>
@@ -2362,18 +2794,22 @@
       <c r="E32" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F32" s="7"/>
-      <c r="G32" s="6">
-        <v>1</v>
-      </c>
+      <c r="F32" s="6">
+        <f>VLOOKUP(E32,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G32" s="7"/>
       <c r="H32" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="6">
+        <v>2</v>
+      </c>
+      <c r="J32" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>48</v>
       </c>
@@ -2390,18 +2826,22 @@
       <c r="E33" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F33" s="7"/>
-      <c r="G33" s="6">
-        <v>1</v>
-      </c>
+      <c r="F33" s="6">
+        <f>VLOOKUP(E33,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G33" s="7"/>
       <c r="H33" s="6">
         <v>1</v>
       </c>
       <c r="I33" s="6">
+        <v>1</v>
+      </c>
+      <c r="J33" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>48</v>
       </c>
@@ -2418,20 +2858,24 @@
       <c r="E34" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G34" s="6">
-        <v>1</v>
+      <c r="F34" s="6">
+        <f>VLOOKUP(E34,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H34" s="6">
         <v>1</v>
       </c>
       <c r="I34" s="6">
+        <v>1</v>
+      </c>
+      <c r="J34" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>48</v>
       </c>
@@ -2448,18 +2892,22 @@
       <c r="E35" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="6">
-        <v>1</v>
-      </c>
+      <c r="F35" s="6">
+        <f>VLOOKUP(E35,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G35" s="7"/>
       <c r="H35" s="6">
         <v>1</v>
       </c>
       <c r="I35" s="6">
+        <v>1</v>
+      </c>
+      <c r="J35" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>48</v>
       </c>
@@ -2476,18 +2924,22 @@
       <c r="E36" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="6">
+      <c r="F36" s="6">
+        <f>VLOOKUP(E36,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G36" s="7"/>
+      <c r="H36" s="6">
         <v>2000</v>
       </c>
-      <c r="H36" s="6">
+      <c r="I36" s="6">
         <v>3000</v>
       </c>
-      <c r="I36" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J36" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>48</v>
       </c>
@@ -2504,18 +2956,22 @@
       <c r="E37" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F37" s="7"/>
-      <c r="G37" s="6">
+      <c r="F37" s="6">
+        <f>VLOOKUP(E37,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G37" s="7"/>
+      <c r="H37" s="6">
         <v>1000</v>
       </c>
-      <c r="H37" s="6">
+      <c r="I37" s="6">
         <v>1500</v>
       </c>
-      <c r="I37" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J37" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>48</v>
       </c>
@@ -2532,18 +2988,22 @@
       <c r="E38" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F38" s="7"/>
-      <c r="G38" s="6">
-        <v>2</v>
-      </c>
+      <c r="F38" s="6">
+        <f>VLOOKUP(E38,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G38" s="7"/>
       <c r="H38" s="6">
+        <v>2</v>
+      </c>
+      <c r="I38" s="6">
         <v>3</v>
       </c>
-      <c r="I38" s="6">
+      <c r="J38" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>48</v>
       </c>
@@ -2560,18 +3020,22 @@
       <c r="E39" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F39" s="7"/>
-      <c r="G39" s="6">
-        <v>1</v>
-      </c>
+      <c r="F39" s="6">
+        <f>VLOOKUP(E39,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G39" s="7"/>
       <c r="H39" s="6">
         <v>1</v>
       </c>
       <c r="I39" s="6">
+        <v>1</v>
+      </c>
+      <c r="J39" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>48</v>
       </c>
@@ -2588,20 +3052,24 @@
       <c r="E40" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G40" s="6">
-        <v>1</v>
+      <c r="F40" s="6">
+        <f>VLOOKUP(E40,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H40" s="6">
         <v>1</v>
       </c>
       <c r="I40" s="6">
+        <v>1</v>
+      </c>
+      <c r="J40" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>48</v>
       </c>
@@ -2618,18 +3086,22 @@
       <c r="E41" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F41" s="7"/>
-      <c r="G41" s="6">
-        <v>1</v>
-      </c>
+      <c r="F41" s="6">
+        <f>VLOOKUP(E41,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G41" s="7"/>
       <c r="H41" s="6">
         <v>1</v>
       </c>
       <c r="I41" s="6">
+        <v>1</v>
+      </c>
+      <c r="J41" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>48</v>
       </c>
@@ -2646,18 +3118,22 @@
       <c r="E42" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="6">
-        <v>1</v>
-      </c>
+      <c r="F42" s="6">
+        <f>VLOOKUP(E42,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="G42" s="7"/>
       <c r="H42" s="6">
         <v>1</v>
       </c>
       <c r="I42" s="6">
+        <v>1</v>
+      </c>
+      <c r="J42" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>58</v>
       </c>
@@ -2674,18 +3150,22 @@
       <c r="E43" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F43" s="7"/>
-      <c r="G43" s="6">
-        <v>100</v>
-      </c>
+      <c r="F43" s="6">
+        <f>VLOOKUP(E43,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G43" s="7"/>
       <c r="H43" s="6">
+        <v>100</v>
+      </c>
+      <c r="I43" s="6">
         <v>200</v>
       </c>
-      <c r="I43" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J43" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>58</v>
       </c>
@@ -2702,18 +3182,22 @@
       <c r="E44" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="7"/>
-      <c r="G44" s="6">
+      <c r="F44" s="6">
+        <f>VLOOKUP(E44,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G44" s="7"/>
+      <c r="H44" s="6">
         <v>50</v>
       </c>
-      <c r="H44" s="6">
-        <v>100</v>
-      </c>
       <c r="I44" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J44" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>58</v>
       </c>
@@ -2730,18 +3214,22 @@
       <c r="E45" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F45" s="7"/>
-      <c r="G45" s="6">
-        <v>1</v>
-      </c>
+      <c r="F45" s="6">
+        <f>VLOOKUP(E45,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G45" s="7"/>
       <c r="H45" s="6">
         <v>1</v>
       </c>
       <c r="I45" s="6">
+        <v>1</v>
+      </c>
+      <c r="J45" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>58</v>
       </c>
@@ -2758,18 +3246,22 @@
       <c r="E46" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F46" s="7"/>
-      <c r="G46" s="6">
-        <v>1</v>
-      </c>
+      <c r="F46" s="6">
+        <f>VLOOKUP(E46,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G46" s="7"/>
       <c r="H46" s="6">
         <v>1</v>
       </c>
       <c r="I46" s="6">
+        <v>1</v>
+      </c>
+      <c r="J46" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>58</v>
       </c>
@@ -2786,20 +3278,24 @@
       <c r="E47" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F47" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G47" s="6">
-        <v>1</v>
+      <c r="F47" s="6">
+        <f>VLOOKUP(E47,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H47" s="6">
         <v>1</v>
       </c>
       <c r="I47" s="6">
+        <v>1</v>
+      </c>
+      <c r="J47" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>58</v>
       </c>
@@ -2816,18 +3312,22 @@
       <c r="E48" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F48" s="7"/>
-      <c r="G48" s="6">
+      <c r="F48" s="6">
+        <f>VLOOKUP(E48,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G48" s="7"/>
+      <c r="H48" s="6">
         <v>500</v>
       </c>
-      <c r="H48" s="6">
+      <c r="I48" s="6">
         <v>800</v>
       </c>
-      <c r="I48" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J48" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>58</v>
       </c>
@@ -2844,18 +3344,22 @@
       <c r="E49" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F49" s="7"/>
-      <c r="G49" s="6">
+      <c r="F49" s="6">
+        <f>VLOOKUP(E49,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G49" s="7"/>
+      <c r="H49" s="6">
         <v>200</v>
       </c>
-      <c r="H49" s="6">
+      <c r="I49" s="6">
         <v>400</v>
       </c>
-      <c r="I49" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J49" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>58</v>
       </c>
@@ -2872,18 +3376,22 @@
       <c r="E50" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F50" s="7"/>
-      <c r="G50" s="6">
-        <v>1</v>
-      </c>
+      <c r="F50" s="6">
+        <f>VLOOKUP(E50,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G50" s="7"/>
       <c r="H50" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="6">
+        <v>2</v>
+      </c>
+      <c r="J50" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>58</v>
       </c>
@@ -2900,18 +3408,22 @@
       <c r="E51" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="6">
-        <v>1</v>
-      </c>
+      <c r="F51" s="6">
+        <f>VLOOKUP(E51,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G51" s="7"/>
       <c r="H51" s="6">
         <v>1</v>
       </c>
       <c r="I51" s="6">
+        <v>1</v>
+      </c>
+      <c r="J51" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>58</v>
       </c>
@@ -2928,20 +3440,24 @@
       <c r="E52" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G52" s="6">
-        <v>1</v>
+      <c r="F52" s="6">
+        <f>VLOOKUP(E52,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H52" s="6">
         <v>1</v>
       </c>
       <c r="I52" s="6">
+        <v>1</v>
+      </c>
+      <c r="J52" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>58</v>
       </c>
@@ -2958,18 +3474,22 @@
       <c r="E53" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F53" s="7"/>
-      <c r="G53" s="6">
-        <v>1</v>
-      </c>
+      <c r="F53" s="6">
+        <f>VLOOKUP(E53,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G53" s="7"/>
       <c r="H53" s="6">
         <v>1</v>
       </c>
       <c r="I53" s="6">
+        <v>1</v>
+      </c>
+      <c r="J53" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>58</v>
       </c>
@@ -2986,18 +3506,22 @@
       <c r="E54" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F54" s="7"/>
-      <c r="G54" s="6">
+      <c r="F54" s="6">
+        <f>VLOOKUP(E54,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G54" s="7"/>
+      <c r="H54" s="6">
         <v>2000</v>
       </c>
-      <c r="H54" s="6">
+      <c r="I54" s="6">
         <v>3000</v>
       </c>
-      <c r="I54" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J54" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>58</v>
       </c>
@@ -3014,18 +3538,22 @@
       <c r="E55" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F55" s="7"/>
-      <c r="G55" s="6">
+      <c r="F55" s="6">
+        <f>VLOOKUP(E55,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G55" s="7"/>
+      <c r="H55" s="6">
         <v>1000</v>
       </c>
-      <c r="H55" s="6">
+      <c r="I55" s="6">
         <v>1500</v>
       </c>
-      <c r="I55" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J55" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>58</v>
       </c>
@@ -3042,18 +3570,22 @@
       <c r="E56" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F56" s="7"/>
-      <c r="G56" s="6">
-        <v>2</v>
-      </c>
+      <c r="F56" s="6">
+        <f>VLOOKUP(E56,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G56" s="7"/>
       <c r="H56" s="6">
+        <v>2</v>
+      </c>
+      <c r="I56" s="6">
         <v>3</v>
       </c>
-      <c r="I56" s="6">
+      <c r="J56" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>58</v>
       </c>
@@ -3070,18 +3602,22 @@
       <c r="E57" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F57" s="7"/>
-      <c r="G57" s="6">
-        <v>1</v>
-      </c>
+      <c r="F57" s="6">
+        <f>VLOOKUP(E57,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G57" s="7"/>
       <c r="H57" s="6">
         <v>1</v>
       </c>
       <c r="I57" s="6">
+        <v>1</v>
+      </c>
+      <c r="J57" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>58</v>
       </c>
@@ -3098,20 +3634,24 @@
       <c r="E58" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G58" s="6">
-        <v>1</v>
+      <c r="F58" s="6">
+        <f>VLOOKUP(E58,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H58" s="6">
         <v>1</v>
       </c>
       <c r="I58" s="6">
+        <v>1</v>
+      </c>
+      <c r="J58" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>58</v>
       </c>
@@ -3128,18 +3668,22 @@
       <c r="E59" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F59" s="7"/>
-      <c r="G59" s="6">
-        <v>1</v>
-      </c>
+      <c r="F59" s="6">
+        <f>VLOOKUP(E59,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G59" s="7"/>
       <c r="H59" s="6">
         <v>1</v>
       </c>
       <c r="I59" s="6">
+        <v>1</v>
+      </c>
+      <c r="J59" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>58</v>
       </c>
@@ -3156,18 +3700,22 @@
       <c r="E60" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F60" s="7"/>
-      <c r="G60" s="6">
-        <v>1</v>
-      </c>
+      <c r="F60" s="6">
+        <f>VLOOKUP(E60,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="G60" s="7"/>
       <c r="H60" s="6">
         <v>1</v>
       </c>
       <c r="I60" s="6">
+        <v>1</v>
+      </c>
+      <c r="J60" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>53</v>
       </c>
@@ -3184,18 +3732,22 @@
       <c r="E61" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F61" s="7"/>
-      <c r="G61" s="6">
-        <v>100</v>
-      </c>
+      <c r="F61" s="6">
+        <f>VLOOKUP(E61,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G61" s="7"/>
       <c r="H61" s="6">
+        <v>100</v>
+      </c>
+      <c r="I61" s="6">
         <v>200</v>
       </c>
-      <c r="I61" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J61" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>53</v>
       </c>
@@ -3212,18 +3764,22 @@
       <c r="E62" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F62" s="7"/>
-      <c r="G62" s="6">
+      <c r="F62" s="6">
+        <f>VLOOKUP(E62,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G62" s="7"/>
+      <c r="H62" s="6">
         <v>50</v>
       </c>
-      <c r="H62" s="6">
-        <v>100</v>
-      </c>
       <c r="I62" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J62" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>53</v>
       </c>
@@ -3240,18 +3796,22 @@
       <c r="E63" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F63" s="7"/>
-      <c r="G63" s="6">
-        <v>1</v>
-      </c>
+      <c r="F63" s="6">
+        <f>VLOOKUP(E63,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G63" s="7"/>
       <c r="H63" s="6">
         <v>1</v>
       </c>
       <c r="I63" s="6">
+        <v>1</v>
+      </c>
+      <c r="J63" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>53</v>
       </c>
@@ -3268,18 +3828,22 @@
       <c r="E64" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F64" s="7"/>
-      <c r="G64" s="6">
-        <v>1</v>
-      </c>
+      <c r="F64" s="6">
+        <f>VLOOKUP(E64,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G64" s="7"/>
       <c r="H64" s="6">
         <v>1</v>
       </c>
       <c r="I64" s="6">
+        <v>1</v>
+      </c>
+      <c r="J64" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>53</v>
       </c>
@@ -3296,20 +3860,24 @@
       <c r="E65" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F65" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G65" s="6">
-        <v>1</v>
+      <c r="F65" s="6">
+        <f>VLOOKUP(E65,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H65" s="6">
         <v>1</v>
       </c>
       <c r="I65" s="6">
+        <v>1</v>
+      </c>
+      <c r="J65" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>53</v>
       </c>
@@ -3326,18 +3894,22 @@
       <c r="E66" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F66" s="7"/>
-      <c r="G66" s="6">
+      <c r="F66" s="6">
+        <f>VLOOKUP(E66,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G66" s="7"/>
+      <c r="H66" s="6">
         <v>500</v>
       </c>
-      <c r="H66" s="6">
+      <c r="I66" s="6">
         <v>800</v>
       </c>
-      <c r="I66" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J66" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>53</v>
       </c>
@@ -3354,18 +3926,22 @@
       <c r="E67" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F67" s="7"/>
-      <c r="G67" s="6">
+      <c r="F67" s="6">
+        <f>VLOOKUP(E67,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G67" s="7"/>
+      <c r="H67" s="6">
         <v>200</v>
       </c>
-      <c r="H67" s="6">
+      <c r="I67" s="6">
         <v>400</v>
       </c>
-      <c r="I67" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J67" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>53</v>
       </c>
@@ -3382,18 +3958,22 @@
       <c r="E68" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F68" s="7"/>
-      <c r="G68" s="6">
-        <v>1</v>
-      </c>
+      <c r="F68" s="6">
+        <f>VLOOKUP(E68,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G68" s="7"/>
       <c r="H68" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68" s="6">
+        <v>2</v>
+      </c>
+      <c r="J68" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>53</v>
       </c>
@@ -3410,18 +3990,22 @@
       <c r="E69" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F69" s="7"/>
-      <c r="G69" s="6">
-        <v>1</v>
-      </c>
+      <c r="F69" s="6">
+        <f>VLOOKUP(E69,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G69" s="7"/>
       <c r="H69" s="6">
         <v>1</v>
       </c>
       <c r="I69" s="6">
+        <v>1</v>
+      </c>
+      <c r="J69" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>53</v>
       </c>
@@ -3438,20 +4022,24 @@
       <c r="E70" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G70" s="6">
-        <v>1</v>
+      <c r="F70" s="6">
+        <f>VLOOKUP(E70,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H70" s="6">
         <v>1</v>
       </c>
       <c r="I70" s="6">
+        <v>1</v>
+      </c>
+      <c r="J70" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>53</v>
       </c>
@@ -3468,18 +4056,22 @@
       <c r="E71" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F71" s="7"/>
-      <c r="G71" s="6">
-        <v>1</v>
-      </c>
+      <c r="F71" s="6">
+        <f>VLOOKUP(E71,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G71" s="7"/>
       <c r="H71" s="6">
         <v>1</v>
       </c>
       <c r="I71" s="6">
+        <v>1</v>
+      </c>
+      <c r="J71" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>53</v>
       </c>
@@ -3496,18 +4088,22 @@
       <c r="E72" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F72" s="7"/>
-      <c r="G72" s="6">
+      <c r="F72" s="6">
+        <f>VLOOKUP(E72,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G72" s="7"/>
+      <c r="H72" s="6">
         <v>2000</v>
       </c>
-      <c r="H72" s="6">
+      <c r="I72" s="6">
         <v>3000</v>
       </c>
-      <c r="I72" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J72" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>53</v>
       </c>
@@ -3524,18 +4120,22 @@
       <c r="E73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F73" s="7"/>
-      <c r="G73" s="6">
+      <c r="F73" s="6">
+        <f>VLOOKUP(E73,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G73" s="7"/>
+      <c r="H73" s="6">
         <v>1000</v>
       </c>
-      <c r="H73" s="6">
+      <c r="I73" s="6">
         <v>1500</v>
       </c>
-      <c r="I73" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J73" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>53</v>
       </c>
@@ -3552,18 +4152,22 @@
       <c r="E74" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F74" s="7"/>
-      <c r="G74" s="6">
-        <v>2</v>
-      </c>
+      <c r="F74" s="6">
+        <f>VLOOKUP(E74,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G74" s="7"/>
       <c r="H74" s="6">
+        <v>2</v>
+      </c>
+      <c r="I74" s="6">
         <v>3</v>
       </c>
-      <c r="I74" s="6">
+      <c r="J74" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>53</v>
       </c>
@@ -3580,18 +4184,22 @@
       <c r="E75" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F75" s="7"/>
-      <c r="G75" s="6">
-        <v>1</v>
-      </c>
+      <c r="F75" s="6">
+        <f>VLOOKUP(E75,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G75" s="7"/>
       <c r="H75" s="6">
         <v>1</v>
       </c>
       <c r="I75" s="6">
+        <v>1</v>
+      </c>
+      <c r="J75" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>53</v>
       </c>
@@ -3608,20 +4216,24 @@
       <c r="E76" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G76" s="6">
-        <v>1</v>
+      <c r="F76" s="6">
+        <f>VLOOKUP(E76,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H76" s="6">
         <v>1</v>
       </c>
       <c r="I76" s="6">
+        <v>1</v>
+      </c>
+      <c r="J76" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>53</v>
       </c>
@@ -3638,18 +4250,22 @@
       <c r="E77" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F77" s="7"/>
-      <c r="G77" s="6">
-        <v>1</v>
-      </c>
+      <c r="F77" s="6">
+        <f>VLOOKUP(E77,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G77" s="7"/>
       <c r="H77" s="6">
         <v>1</v>
       </c>
       <c r="I77" s="6">
+        <v>1</v>
+      </c>
+      <c r="J77" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>53</v>
       </c>
@@ -3666,18 +4282,22 @@
       <c r="E78" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F78" s="7"/>
-      <c r="G78" s="6">
-        <v>1</v>
-      </c>
+      <c r="F78" s="6">
+        <f>VLOOKUP(E78,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="G78" s="7"/>
       <c r="H78" s="6">
         <v>1</v>
       </c>
       <c r="I78" s="6">
+        <v>1</v>
+      </c>
+      <c r="J78" s="6">
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
         <v>63</v>
       </c>
@@ -3694,18 +4314,22 @@
       <c r="E79" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F79" s="7"/>
-      <c r="G79" s="6">
-        <v>100</v>
-      </c>
+      <c r="F79" s="6">
+        <f>VLOOKUP(E79,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G79" s="7"/>
       <c r="H79" s="6">
+        <v>100</v>
+      </c>
+      <c r="I79" s="6">
         <v>200</v>
       </c>
-      <c r="I79" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J79" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>63</v>
       </c>
@@ -3722,18 +4346,22 @@
       <c r="E80" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F80" s="7"/>
-      <c r="G80" s="6">
+      <c r="F80" s="6">
+        <f>VLOOKUP(E80,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G80" s="7"/>
+      <c r="H80" s="6">
         <v>50</v>
       </c>
-      <c r="H80" s="6">
-        <v>100</v>
-      </c>
       <c r="I80" s="6">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J80" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>63</v>
       </c>
@@ -3750,18 +4378,22 @@
       <c r="E81" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F81" s="7"/>
-      <c r="G81" s="6">
-        <v>1</v>
-      </c>
+      <c r="F81" s="6">
+        <f>VLOOKUP(E81,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G81" s="7"/>
       <c r="H81" s="6">
         <v>1</v>
       </c>
       <c r="I81" s="6">
+        <v>1</v>
+      </c>
+      <c r="J81" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>63</v>
       </c>
@@ -3778,18 +4410,22 @@
       <c r="E82" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F82" s="7"/>
-      <c r="G82" s="6">
-        <v>1</v>
-      </c>
+      <c r="F82" s="6">
+        <f>VLOOKUP(E82,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G82" s="7"/>
       <c r="H82" s="6">
         <v>1</v>
       </c>
       <c r="I82" s="6">
+        <v>1</v>
+      </c>
+      <c r="J82" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>63</v>
       </c>
@@ -3806,20 +4442,24 @@
       <c r="E83" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F83" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G83" s="6">
-        <v>1</v>
+      <c r="F83" s="6">
+        <f>VLOOKUP(E83,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H83" s="6">
         <v>1</v>
       </c>
       <c r="I83" s="6">
+        <v>1</v>
+      </c>
+      <c r="J83" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>63</v>
       </c>
@@ -3836,18 +4476,22 @@
       <c r="E84" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F84" s="7"/>
-      <c r="G84" s="6">
+      <c r="F84" s="6">
+        <f>VLOOKUP(E84,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G84" s="7"/>
+      <c r="H84" s="6">
         <v>500</v>
       </c>
-      <c r="H84" s="6">
+      <c r="I84" s="6">
         <v>800</v>
       </c>
-      <c r="I84" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J84" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>63</v>
       </c>
@@ -3864,18 +4508,22 @@
       <c r="E85" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F85" s="7"/>
-      <c r="G85" s="6">
+      <c r="F85" s="6">
+        <f>VLOOKUP(E85,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G85" s="7"/>
+      <c r="H85" s="6">
         <v>200</v>
       </c>
-      <c r="H85" s="6">
+      <c r="I85" s="6">
         <v>400</v>
       </c>
-      <c r="I85" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J85" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>63</v>
       </c>
@@ -3892,18 +4540,22 @@
       <c r="E86" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F86" s="7"/>
-      <c r="G86" s="6">
-        <v>1</v>
-      </c>
+      <c r="F86" s="6">
+        <f>VLOOKUP(E86,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G86" s="7"/>
       <c r="H86" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="6">
+        <v>2</v>
+      </c>
+      <c r="J86" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>63</v>
       </c>
@@ -3920,18 +4572,22 @@
       <c r="E87" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F87" s="7"/>
-      <c r="G87" s="6">
-        <v>1</v>
-      </c>
+      <c r="F87" s="6">
+        <f>VLOOKUP(E87,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G87" s="7"/>
       <c r="H87" s="6">
         <v>1</v>
       </c>
       <c r="I87" s="6">
+        <v>1</v>
+      </c>
+      <c r="J87" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>63</v>
       </c>
@@ -3948,20 +4604,24 @@
       <c r="E88" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G88" s="6">
-        <v>1</v>
+      <c r="F88" s="6">
+        <f>VLOOKUP(E88,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H88" s="6">
         <v>1</v>
       </c>
       <c r="I88" s="6">
+        <v>1</v>
+      </c>
+      <c r="J88" s="6">
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>63</v>
       </c>
@@ -3978,18 +4638,22 @@
       <c r="E89" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F89" s="7"/>
-      <c r="G89" s="6">
-        <v>1</v>
-      </c>
+      <c r="F89" s="6">
+        <f>VLOOKUP(E89,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G89" s="7"/>
       <c r="H89" s="6">
         <v>1</v>
       </c>
       <c r="I89" s="6">
+        <v>1</v>
+      </c>
+      <c r="J89" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>63</v>
       </c>
@@ -4006,18 +4670,22 @@
       <c r="E90" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F90" s="7"/>
-      <c r="G90" s="6">
+      <c r="F90" s="6">
+        <f>VLOOKUP(E90,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G90" s="7"/>
+      <c r="H90" s="6">
         <v>2000</v>
       </c>
-      <c r="H90" s="6">
+      <c r="I90" s="6">
         <v>3000</v>
       </c>
-      <c r="I90" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J90" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>63</v>
       </c>
@@ -4034,18 +4702,22 @@
       <c r="E91" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F91" s="7"/>
-      <c r="G91" s="6">
+      <c r="F91" s="6">
+        <f>VLOOKUP(E91,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G91" s="7"/>
+      <c r="H91" s="6">
         <v>1000</v>
       </c>
-      <c r="H91" s="6">
+      <c r="I91" s="6">
         <v>1500</v>
       </c>
-      <c r="I91" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J91" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>63</v>
       </c>
@@ -4062,18 +4734,22 @@
       <c r="E92" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F92" s="7"/>
-      <c r="G92" s="6">
-        <v>2</v>
-      </c>
+      <c r="F92" s="6">
+        <f>VLOOKUP(E92,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G92" s="7"/>
       <c r="H92" s="6">
+        <v>2</v>
+      </c>
+      <c r="I92" s="6">
         <v>3</v>
       </c>
-      <c r="I92" s="6">
+      <c r="J92" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
         <v>63</v>
       </c>
@@ -4090,18 +4766,22 @@
       <c r="E93" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F93" s="7"/>
-      <c r="G93" s="6">
-        <v>1</v>
-      </c>
+      <c r="F93" s="6">
+        <f>VLOOKUP(E93,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="G93" s="7"/>
       <c r="H93" s="6">
         <v>1</v>
       </c>
       <c r="I93" s="6">
+        <v>1</v>
+      </c>
+      <c r="J93" s="6">
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>63</v>
       </c>
@@ -4118,20 +4798,24 @@
       <c r="E94" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G94" s="6">
-        <v>1</v>
+      <c r="F94" s="6">
+        <f>VLOOKUP(E94,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>7</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="H94" s="6">
         <v>1</v>
       </c>
       <c r="I94" s="6">
+        <v>1</v>
+      </c>
+      <c r="J94" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
         <v>63</v>
       </c>
@@ -4148,18 +4832,22 @@
       <c r="E95" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F95" s="7"/>
-      <c r="G95" s="6">
-        <v>1</v>
-      </c>
+      <c r="F95" s="6">
+        <f>VLOOKUP(E95,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="G95" s="7"/>
       <c r="H95" s="6">
         <v>1</v>
       </c>
       <c r="I95" s="6">
+        <v>1</v>
+      </c>
+      <c r="J95" s="6">
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
         <v>63</v>
       </c>
@@ -4176,15 +4864,204 @@
       <c r="E96" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F96" s="7"/>
-      <c r="G96" s="6">
-        <v>1</v>
-      </c>
+      <c r="F96" s="6">
+        <f>VLOOKUP(E96,Overview!$F$9:$G$24,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="G96" s="7"/>
       <c r="H96" s="6">
         <v>1</v>
       </c>
       <c r="I96" s="6">
+        <v>1</v>
+      </c>
+      <c r="J96" s="6">
         <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D836302-B302-44BC-BDF2-498BD94CAC4F}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6">
+        <v>1200</v>
+      </c>
+      <c r="C4" s="6">
+        <v>1200</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6">
+        <v>2400</v>
+      </c>
+      <c r="C5" s="6">
+        <v>3600</v>
+      </c>
+      <c r="D5" s="6">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6">
+        <v>4800</v>
+      </c>
+      <c r="C6" s="6">
+        <v>8400</v>
+      </c>
+      <c r="D6" s="6">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6">
+        <v>8400</v>
+      </c>
+      <c r="C7" s="6">
+        <v>16800</v>
+      </c>
+      <c r="D7" s="6">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6">
+        <v>13200</v>
+      </c>
+      <c r="C8" s="6">
+        <v>30000</v>
+      </c>
+      <c r="D8" s="6">
+        <v>129600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6">
+        <v>18000</v>
+      </c>
+      <c r="C9" s="6">
+        <v>48000</v>
+      </c>
+      <c r="D9" s="6">
+        <v>172800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6">
+        <v>22800</v>
+      </c>
+      <c r="C10" s="6">
+        <v>70800</v>
+      </c>
+      <c r="D10" s="6">
+        <v>259200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6">
+        <v>31200</v>
+      </c>
+      <c r="C11" s="6">
+        <v>102000</v>
+      </c>
+      <c r="D11" s="6">
+        <v>345600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6">
+        <v>42000</v>
+      </c>
+      <c r="C12" s="6">
+        <v>144000</v>
+      </c>
+      <c r="D12" s="6">
+        <v>518400</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/castle.xlsx
+++ b/ExcelToJSONConverter/excel/castle.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25158BB-2BBF-4668-8A4B-B3066C87B63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4EA72-ADC6-4C4D-BAFD-734675F0B17A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -98,18 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>count_batch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>max_amount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -118,22 +106,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>upgrade_duration</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>stat_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stat_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Palace</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -414,6 +390,30 @@
   </si>
   <si>
     <t>upgrade_seconds</t>
+  </si>
+  <si>
+    <t>stat_type_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stat_type_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>req_stat_value_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>req_stat_value_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chracter_slot_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_seconds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -538,7 +538,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -574,6 +574,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1001,13 +1004,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1015,13 +1018,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G10">
         <f>G9+1</f>
@@ -1030,13 +1033,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G11">
         <f t="shared" ref="G11:G24" si="0">G10+1</f>
@@ -1045,13 +1048,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G12">
         <f t="shared" si="0"/>
@@ -1060,13 +1063,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
@@ -1075,7 +1078,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F14" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
@@ -1084,7 +1087,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
@@ -1093,13 +1096,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G16">
         <f t="shared" si="0"/>
@@ -1108,13 +1111,13 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
@@ -1123,13 +1126,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
@@ -1138,13 +1141,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G19">
         <f t="shared" si="0"/>
@@ -1153,13 +1156,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
@@ -1168,7 +1171,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F21" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G21">
         <f t="shared" si="0"/>
@@ -1177,7 +1180,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F22" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G22">
         <f t="shared" si="0"/>
@@ -1186,7 +1189,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F23" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G23">
         <f t="shared" si="0"/>
@@ -1195,7 +1198,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="F24" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G24">
         <f t="shared" si="0"/>
@@ -1223,10 +1226,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -1242,84 +1245,85 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1327,25 +1331,25 @@
         <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1370,114 +1374,256 @@
       <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K2">
-        <v>70</v>
-      </c>
-      <c r="L2">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="12">
+        <v>1</v>
+      </c>
+      <c r="C3" s="10">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="D3" s="10">
         <v>80</v>
       </c>
-      <c r="D3">
-        <v>80</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="E3" s="10">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
         <v>1000</v>
       </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <f>K2/L2</f>
-        <v>0.875</v>
-      </c>
-      <c r="L3">
-        <f>J3+J3*K3</f>
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="str">
+      <c r="H3" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="str">
         <f>A3</f>
         <v>NONE</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="12">
         <f>B3+1</f>
         <v>2</v>
       </c>
-      <c r="C4" s="3">
-        <v>160</v>
-      </c>
-      <c r="D4">
-        <v>160</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>60</v>
-      </c>
-      <c r="G4">
+      <c r="C4" s="10">
+        <v>150</v>
+      </c>
+      <c r="D4" s="10">
+        <v>150</v>
+      </c>
+      <c r="E4" s="10">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
         <v>2000</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="str">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="str">
         <f>A4</f>
         <v>NONE</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="12">
         <f>B4+1</f>
         <v>3</v>
       </c>
-      <c r="C5" s="3">
-        <v>240</v>
-      </c>
-      <c r="D5">
-        <v>240</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>120</v>
-      </c>
-      <c r="G5">
+      <c r="C5" s="10">
+        <v>210</v>
+      </c>
+      <c r="D5" s="10">
+        <v>210</v>
+      </c>
+      <c r="E5" s="10">
+        <v>2</v>
+      </c>
+      <c r="F5" s="10">
+        <v>7200</v>
+      </c>
+      <c r="G5" s="9">
         <v>3000</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="str">
+        <f t="shared" ref="A6:A12" si="0">A5</f>
+        <v>NONE</v>
+      </c>
+      <c r="B6" s="12">
+        <f t="shared" ref="B6:B12" si="1">B5+1</f>
+        <v>4</v>
+      </c>
+      <c r="C6" s="10">
+        <v>260</v>
+      </c>
+      <c r="D6" s="10">
+        <v>260</v>
+      </c>
+      <c r="E6" s="10">
+        <v>2</v>
+      </c>
+      <c r="F6" s="10">
+        <v>43200</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>NONE</v>
+      </c>
+      <c r="B7" s="12">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C7" s="10">
+        <v>310</v>
+      </c>
+      <c r="D7" s="10">
+        <v>310</v>
+      </c>
+      <c r="E7" s="10">
+        <v>3</v>
+      </c>
+      <c r="F7" s="10">
+        <v>86400</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>NONE</v>
+      </c>
+      <c r="B8" s="12">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C8" s="10">
+        <v>360</v>
+      </c>
+      <c r="D8" s="10">
+        <v>360</v>
+      </c>
+      <c r="E8" s="10">
+        <v>3</v>
+      </c>
+      <c r="F8" s="10">
+        <v>129600</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>NONE</v>
+      </c>
+      <c r="B9" s="12">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C9" s="10">
+        <v>410</v>
+      </c>
+      <c r="D9" s="10">
+        <v>410</v>
+      </c>
+      <c r="E9" s="10">
+        <v>4</v>
+      </c>
+      <c r="F9" s="10">
+        <v>172800</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>NONE</v>
+      </c>
+      <c r="B10" s="12">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C10" s="10">
+        <v>460</v>
+      </c>
+      <c r="D10" s="10">
+        <v>460</v>
+      </c>
+      <c r="E10" s="10">
+        <v>4</v>
+      </c>
+      <c r="F10" s="10">
+        <v>259200</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>NONE</v>
+      </c>
+      <c r="B11" s="12">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="C11" s="10">
+        <v>500</v>
+      </c>
+      <c r="D11" s="10">
+        <v>500</v>
+      </c>
+      <c r="E11" s="10">
+        <v>5</v>
+      </c>
+      <c r="F11" s="10">
+        <v>345600</v>
+      </c>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>NONE</v>
+      </c>
+      <c r="B12" s="12">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="C12" s="10">
+        <v>600</v>
+      </c>
+      <c r="D12" s="10">
+        <v>600</v>
+      </c>
+      <c r="E12" s="10">
+        <v>6</v>
+      </c>
+      <c r="F12" s="10">
+        <v>518400</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:A41">
@@ -1502,16 +1648,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1519,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>0</v>
@@ -1530,10 +1676,10 @@
     </row>
     <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C3" s="6">
         <v>0</v>
@@ -1542,10 +1688,10 @@
     </row>
     <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C4" s="6">
         <v>0</v>
@@ -1554,10 +1700,10 @@
     </row>
     <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
@@ -1566,10 +1712,10 @@
     </row>
     <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -1578,10 +1724,10 @@
     </row>
     <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C7" s="6">
         <v>3</v>
@@ -1590,10 +1736,10 @@
     </row>
     <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C8" s="6">
         <v>3</v>
@@ -1602,10 +1748,10 @@
     </row>
     <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C9" s="6">
         <v>2</v>
@@ -1614,10 +1760,10 @@
     </row>
     <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C10" s="6">
         <v>2</v>
@@ -1626,10 +1772,10 @@
     </row>
     <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C11" s="6">
         <v>4</v>
@@ -1638,10 +1784,10 @@
     </row>
     <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C12" s="6">
         <v>4</v>
@@ -1669,19 +1815,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1692,18 +1838,18 @@
         <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B3" s="10">
         <f>VLOOKUP(A3,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1721,7 +1867,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B4" s="10">
         <f>VLOOKUP(A4,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1739,7 +1885,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B5" s="10">
         <f>VLOOKUP(A5,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1781,34 +1927,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1820,7 +1966,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>0</v>
@@ -1832,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>0</v>
@@ -1843,10 +1989,10 @@
     </row>
     <row r="3" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="6">
         <f>VLOOKUP(B3,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1856,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F3" s="6">
         <f>VLOOKUP(E3,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -1875,10 +2021,10 @@
     </row>
     <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C4" s="6">
         <f>VLOOKUP(B4,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1888,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F4" s="6">
         <f>VLOOKUP(E4,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -1907,10 +2053,10 @@
     </row>
     <row r="5" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" s="6">
         <f>VLOOKUP(B5,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1920,7 +2066,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F5" s="6">
         <f>VLOOKUP(E5,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -1939,10 +2085,10 @@
     </row>
     <row r="6" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" s="6">
         <f>VLOOKUP(B6,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1952,7 +2098,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F6" s="6">
         <f>VLOOKUP(E6,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -1971,10 +2117,10 @@
     </row>
     <row r="7" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" s="6">
         <f>VLOOKUP(B7,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -1984,7 +2130,7 @@
         <v>50</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F7" s="6">
         <f>VLOOKUP(E7,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2003,10 +2149,10 @@
     </row>
     <row r="8" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C8" s="6">
         <f>VLOOKUP(B8,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2016,7 +2162,7 @@
         <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F8" s="6">
         <f>VLOOKUP(E8,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2035,10 +2181,10 @@
     </row>
     <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" s="6">
         <f>VLOOKUP(B9,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2048,14 +2194,14 @@
         <v>100</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F9" s="6">
         <f>VLOOKUP(E9,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H9" s="6">
         <v>1</v>
@@ -2069,10 +2215,10 @@
     </row>
     <row r="10" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C10" s="6">
         <f>VLOOKUP(B10,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2082,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F10" s="6">
         <f>VLOOKUP(E10,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2101,10 +2247,10 @@
     </row>
     <row r="11" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C11" s="6">
         <f>VLOOKUP(B11,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2114,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F11" s="6">
         <f>VLOOKUP(E11,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2133,10 +2279,10 @@
     </row>
     <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C12" s="6">
         <f>VLOOKUP(B12,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2146,7 +2292,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F12" s="6">
         <f>VLOOKUP(E12,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2165,10 +2311,10 @@
     </row>
     <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C13" s="6">
         <f>VLOOKUP(B13,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2178,7 +2324,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F13" s="6">
         <f>VLOOKUP(E13,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2197,10 +2343,10 @@
     </row>
     <row r="14" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C14" s="6">
         <f>VLOOKUP(B14,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2210,7 +2356,7 @@
         <v>50</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F14" s="6">
         <f>VLOOKUP(E14,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2229,10 +2375,10 @@
     </row>
     <row r="15" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C15" s="6">
         <f>VLOOKUP(B15,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2242,7 +2388,7 @@
         <v>50</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F15" s="6">
         <f>VLOOKUP(E15,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2261,10 +2407,10 @@
     </row>
     <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C16" s="6">
         <f>VLOOKUP(B16,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2274,14 +2420,14 @@
         <v>75</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6">
         <f>VLOOKUP(E16,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H16" s="6">
         <v>1</v>
@@ -2295,10 +2441,10 @@
     </row>
     <row r="17" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C17" s="6">
         <f>VLOOKUP(B17,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2308,7 +2454,7 @@
         <v>100</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F17" s="6">
         <f>VLOOKUP(E17,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2327,10 +2473,10 @@
     </row>
     <row r="18" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C18" s="6">
         <f>VLOOKUP(B18,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2340,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F18" s="6">
         <f>VLOOKUP(E18,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2359,10 +2505,10 @@
     </row>
     <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C19" s="6">
         <f>VLOOKUP(B19,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2372,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F19" s="6">
         <f>VLOOKUP(E19,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2391,10 +2537,10 @@
     </row>
     <row r="20" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C20" s="6">
         <f>VLOOKUP(B20,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2404,7 +2550,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F20" s="6">
         <f>VLOOKUP(E20,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2423,10 +2569,10 @@
     </row>
     <row r="21" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C21" s="6">
         <f>VLOOKUP(B21,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2436,7 +2582,7 @@
         <v>50</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F21" s="6">
         <f>VLOOKUP(E21,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2455,10 +2601,10 @@
     </row>
     <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C22" s="6">
         <f>VLOOKUP(B22,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2468,14 +2614,14 @@
         <v>75</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F22" s="6">
         <f>VLOOKUP(E22,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H22" s="6">
         <v>1</v>
@@ -2489,10 +2635,10 @@
     </row>
     <row r="23" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C23" s="6">
         <f>VLOOKUP(B23,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2502,7 +2648,7 @@
         <v>90</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F23" s="6">
         <f>VLOOKUP(E23,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2521,10 +2667,10 @@
     </row>
     <row r="24" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C24" s="6">
         <f>VLOOKUP(B24,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2534,7 +2680,7 @@
         <v>100</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F24" s="6">
         <f>VLOOKUP(E24,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2553,10 +2699,10 @@
     </row>
     <row r="25" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C25" s="6">
         <f>VLOOKUP(B25,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2566,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F25" s="6">
         <f>VLOOKUP(E25,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2585,10 +2731,10 @@
     </row>
     <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C26" s="6">
         <f>VLOOKUP(B26,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2598,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F26" s="6">
         <f>VLOOKUP(E26,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2617,10 +2763,10 @@
     </row>
     <row r="27" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C27" s="6">
         <f>VLOOKUP(B27,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2630,7 +2776,7 @@
         <v>25</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F27" s="6">
         <f>VLOOKUP(E27,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2649,10 +2795,10 @@
     </row>
     <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C28" s="6">
         <f>VLOOKUP(B28,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2662,7 +2808,7 @@
         <v>50</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F28" s="6">
         <f>VLOOKUP(E28,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2681,10 +2827,10 @@
     </row>
     <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C29" s="6">
         <f>VLOOKUP(B29,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2694,14 +2840,14 @@
         <v>100</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F29" s="6">
         <f>VLOOKUP(E29,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H29" s="6">
         <v>1</v>
@@ -2715,10 +2861,10 @@
     </row>
     <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C30" s="6">
         <f>VLOOKUP(B30,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2728,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F30" s="6">
         <f>VLOOKUP(E30,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2747,10 +2893,10 @@
     </row>
     <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C31" s="6">
         <f>VLOOKUP(B31,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2760,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F31" s="6">
         <f>VLOOKUP(E31,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2779,10 +2925,10 @@
     </row>
     <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C32" s="6">
         <f>VLOOKUP(B32,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2792,7 +2938,7 @@
         <v>25</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F32" s="6">
         <f>VLOOKUP(E32,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2811,10 +2957,10 @@
     </row>
     <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C33" s="6">
         <f>VLOOKUP(B33,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2824,7 +2970,7 @@
         <v>50</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F33" s="6">
         <f>VLOOKUP(E33,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2843,10 +2989,10 @@
     </row>
     <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C34" s="6">
         <f>VLOOKUP(B34,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2856,14 +3002,14 @@
         <v>75</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F34" s="6">
         <f>VLOOKUP(E34,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H34" s="6">
         <v>1</v>
@@ -2877,10 +3023,10 @@
     </row>
     <row r="35" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C35" s="6">
         <f>VLOOKUP(B35,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2890,7 +3036,7 @@
         <v>100</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F35" s="6">
         <f>VLOOKUP(E35,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2909,10 +3055,10 @@
     </row>
     <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C36" s="6">
         <f>VLOOKUP(B36,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2922,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F36" s="6">
         <f>VLOOKUP(E36,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2941,10 +3087,10 @@
     </row>
     <row r="37" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C37" s="6">
         <f>VLOOKUP(B37,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2954,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F37" s="6">
         <f>VLOOKUP(E37,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -2973,10 +3119,10 @@
     </row>
     <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C38" s="6">
         <f>VLOOKUP(B38,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -2986,7 +3132,7 @@
         <v>25</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F38" s="6">
         <f>VLOOKUP(E38,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3005,10 +3151,10 @@
     </row>
     <row r="39" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C39" s="6">
         <f>VLOOKUP(B39,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3018,7 +3164,7 @@
         <v>50</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F39" s="6">
         <f>VLOOKUP(E39,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3037,10 +3183,10 @@
     </row>
     <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C40" s="6">
         <f>VLOOKUP(B40,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3050,14 +3196,14 @@
         <v>75</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F40" s="6">
         <f>VLOOKUP(E40,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H40" s="6">
         <v>1</v>
@@ -3071,10 +3217,10 @@
     </row>
     <row r="41" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C41" s="6">
         <f>VLOOKUP(B41,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3084,7 +3230,7 @@
         <v>90</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F41" s="6">
         <f>VLOOKUP(E41,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3103,10 +3249,10 @@
     </row>
     <row r="42" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C42" s="6">
         <f>VLOOKUP(B42,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3116,7 +3262,7 @@
         <v>100</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F42" s="6">
         <f>VLOOKUP(E42,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3135,10 +3281,10 @@
     </row>
     <row r="43" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C43" s="6">
         <f>VLOOKUP(B43,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3148,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F43" s="6">
         <f>VLOOKUP(E43,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3167,10 +3313,10 @@
     </row>
     <row r="44" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C44" s="6">
         <f>VLOOKUP(B44,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3180,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F44" s="6">
         <f>VLOOKUP(E44,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3199,10 +3345,10 @@
     </row>
     <row r="45" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C45" s="6">
         <f>VLOOKUP(B45,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3212,7 +3358,7 @@
         <v>25</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F45" s="6">
         <f>VLOOKUP(E45,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3231,10 +3377,10 @@
     </row>
     <row r="46" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C46" s="6">
         <f>VLOOKUP(B46,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3244,7 +3390,7 @@
         <v>50</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F46" s="6">
         <f>VLOOKUP(E46,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3263,10 +3409,10 @@
     </row>
     <row r="47" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C47" s="6">
         <f>VLOOKUP(B47,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3276,14 +3422,14 @@
         <v>100</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F47" s="6">
         <f>VLOOKUP(E47,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H47" s="6">
         <v>1</v>
@@ -3297,10 +3443,10 @@
     </row>
     <row r="48" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C48" s="6">
         <f>VLOOKUP(B48,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3310,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F48" s="6">
         <f>VLOOKUP(E48,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3329,10 +3475,10 @@
     </row>
     <row r="49" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C49" s="6">
         <f>VLOOKUP(B49,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3342,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F49" s="6">
         <f>VLOOKUP(E49,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3361,10 +3507,10 @@
     </row>
     <row r="50" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C50" s="6">
         <f>VLOOKUP(B50,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3374,7 +3520,7 @@
         <v>25</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F50" s="6">
         <f>VLOOKUP(E50,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3393,10 +3539,10 @@
     </row>
     <row r="51" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C51" s="6">
         <f>VLOOKUP(B51,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3406,7 +3552,7 @@
         <v>50</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F51" s="6">
         <f>VLOOKUP(E51,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3425,10 +3571,10 @@
     </row>
     <row r="52" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C52" s="6">
         <f>VLOOKUP(B52,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3438,14 +3584,14 @@
         <v>75</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F52" s="6">
         <f>VLOOKUP(E52,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H52" s="6">
         <v>1</v>
@@ -3459,10 +3605,10 @@
     </row>
     <row r="53" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C53" s="6">
         <f>VLOOKUP(B53,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3472,7 +3618,7 @@
         <v>100</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F53" s="6">
         <f>VLOOKUP(E53,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3491,10 +3637,10 @@
     </row>
     <row r="54" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C54" s="6">
         <f>VLOOKUP(B54,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3504,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F54" s="6">
         <f>VLOOKUP(E54,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3523,10 +3669,10 @@
     </row>
     <row r="55" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C55" s="6">
         <f>VLOOKUP(B55,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3536,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F55" s="6">
         <f>VLOOKUP(E55,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3555,10 +3701,10 @@
     </row>
     <row r="56" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C56" s="6">
         <f>VLOOKUP(B56,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3568,7 +3714,7 @@
         <v>25</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F56" s="6">
         <f>VLOOKUP(E56,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3587,10 +3733,10 @@
     </row>
     <row r="57" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C57" s="6">
         <f>VLOOKUP(B57,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3600,7 +3746,7 @@
         <v>50</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F57" s="6">
         <f>VLOOKUP(E57,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3619,10 +3765,10 @@
     </row>
     <row r="58" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C58" s="6">
         <f>VLOOKUP(B58,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3632,14 +3778,14 @@
         <v>75</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F58" s="6">
         <f>VLOOKUP(E58,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H58" s="6">
         <v>1</v>
@@ -3653,10 +3799,10 @@
     </row>
     <row r="59" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C59" s="6">
         <f>VLOOKUP(B59,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3666,7 +3812,7 @@
         <v>90</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F59" s="6">
         <f>VLOOKUP(E59,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3685,10 +3831,10 @@
     </row>
     <row r="60" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C60" s="6">
         <f>VLOOKUP(B60,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3698,7 +3844,7 @@
         <v>100</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F60" s="6">
         <f>VLOOKUP(E60,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3717,10 +3863,10 @@
     </row>
     <row r="61" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C61" s="6">
         <f>VLOOKUP(B61,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3730,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F61" s="6">
         <f>VLOOKUP(E61,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3749,10 +3895,10 @@
     </row>
     <row r="62" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C62" s="6">
         <f>VLOOKUP(B62,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3762,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F62" s="6">
         <f>VLOOKUP(E62,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3781,10 +3927,10 @@
     </row>
     <row r="63" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C63" s="6">
         <f>VLOOKUP(B63,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3794,7 +3940,7 @@
         <v>25</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F63" s="6">
         <f>VLOOKUP(E63,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3813,10 +3959,10 @@
     </row>
     <row r="64" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C64" s="6">
         <f>VLOOKUP(B64,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3826,7 +3972,7 @@
         <v>50</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F64" s="6">
         <f>VLOOKUP(E64,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3845,10 +3991,10 @@
     </row>
     <row r="65" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C65" s="6">
         <f>VLOOKUP(B65,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3858,14 +4004,14 @@
         <v>100</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F65" s="6">
         <f>VLOOKUP(E65,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H65" s="6">
         <v>1</v>
@@ -3879,10 +4025,10 @@
     </row>
     <row r="66" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C66" s="6">
         <f>VLOOKUP(B66,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3892,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F66" s="6">
         <f>VLOOKUP(E66,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3911,10 +4057,10 @@
     </row>
     <row r="67" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C67" s="6">
         <f>VLOOKUP(B67,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3924,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F67" s="6">
         <f>VLOOKUP(E67,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3943,10 +4089,10 @@
     </row>
     <row r="68" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C68" s="6">
         <f>VLOOKUP(B68,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3956,7 +4102,7 @@
         <v>25</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F68" s="6">
         <f>VLOOKUP(E68,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -3975,10 +4121,10 @@
     </row>
     <row r="69" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C69" s="6">
         <f>VLOOKUP(B69,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -3988,7 +4134,7 @@
         <v>50</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F69" s="6">
         <f>VLOOKUP(E69,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4007,10 +4153,10 @@
     </row>
     <row r="70" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C70" s="6">
         <f>VLOOKUP(B70,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4020,14 +4166,14 @@
         <v>75</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F70" s="6">
         <f>VLOOKUP(E70,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H70" s="6">
         <v>1</v>
@@ -4041,10 +4187,10 @@
     </row>
     <row r="71" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C71" s="6">
         <f>VLOOKUP(B71,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4054,7 +4200,7 @@
         <v>100</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F71" s="6">
         <f>VLOOKUP(E71,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4073,10 +4219,10 @@
     </row>
     <row r="72" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C72" s="6">
         <f>VLOOKUP(B72,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4086,7 +4232,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F72" s="6">
         <f>VLOOKUP(E72,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4105,10 +4251,10 @@
     </row>
     <row r="73" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C73" s="6">
         <f>VLOOKUP(B73,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4118,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F73" s="6">
         <f>VLOOKUP(E73,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4137,10 +4283,10 @@
     </row>
     <row r="74" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C74" s="6">
         <f>VLOOKUP(B74,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4150,7 +4296,7 @@
         <v>25</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F74" s="6">
         <f>VLOOKUP(E74,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4169,10 +4315,10 @@
     </row>
     <row r="75" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C75" s="6">
         <f>VLOOKUP(B75,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4182,7 +4328,7 @@
         <v>50</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F75" s="6">
         <f>VLOOKUP(E75,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4201,10 +4347,10 @@
     </row>
     <row r="76" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C76" s="6">
         <f>VLOOKUP(B76,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4214,14 +4360,14 @@
         <v>75</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F76" s="6">
         <f>VLOOKUP(E76,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H76" s="6">
         <v>1</v>
@@ -4235,10 +4381,10 @@
     </row>
     <row r="77" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C77" s="6">
         <f>VLOOKUP(B77,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4248,7 +4394,7 @@
         <v>90</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F77" s="6">
         <f>VLOOKUP(E77,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4267,10 +4413,10 @@
     </row>
     <row r="78" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C78" s="6">
         <f>VLOOKUP(B78,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4280,7 +4426,7 @@
         <v>100</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F78" s="6">
         <f>VLOOKUP(E78,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4299,10 +4445,10 @@
     </row>
     <row r="79" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C79" s="6">
         <f>VLOOKUP(B79,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4312,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F79" s="6">
         <f>VLOOKUP(E79,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4331,10 +4477,10 @@
     </row>
     <row r="80" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C80" s="6">
         <f>VLOOKUP(B80,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4344,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F80" s="6">
         <f>VLOOKUP(E80,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4363,10 +4509,10 @@
     </row>
     <row r="81" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C81" s="6">
         <f>VLOOKUP(B81,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4376,7 +4522,7 @@
         <v>25</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F81" s="6">
         <f>VLOOKUP(E81,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4395,10 +4541,10 @@
     </row>
     <row r="82" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C82" s="6">
         <f>VLOOKUP(B82,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4408,7 +4554,7 @@
         <v>50</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F82" s="6">
         <f>VLOOKUP(E82,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4427,10 +4573,10 @@
     </row>
     <row r="83" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C83" s="6">
         <f>VLOOKUP(B83,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4440,14 +4586,14 @@
         <v>100</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F83" s="6">
         <f>VLOOKUP(E83,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>5</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H83" s="6">
         <v>1</v>
@@ -4461,10 +4607,10 @@
     </row>
     <row r="84" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C84" s="6">
         <f>VLOOKUP(B84,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4474,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F84" s="6">
         <f>VLOOKUP(E84,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4493,10 +4639,10 @@
     </row>
     <row r="85" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C85" s="6">
         <f>VLOOKUP(B85,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4506,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F85" s="6">
         <f>VLOOKUP(E85,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4525,10 +4671,10 @@
     </row>
     <row r="86" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C86" s="6">
         <f>VLOOKUP(B86,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4538,7 +4684,7 @@
         <v>25</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F86" s="6">
         <f>VLOOKUP(E86,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4557,10 +4703,10 @@
     </row>
     <row r="87" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C87" s="6">
         <f>VLOOKUP(B87,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4570,7 +4716,7 @@
         <v>50</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F87" s="6">
         <f>VLOOKUP(E87,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4589,10 +4735,10 @@
     </row>
     <row r="88" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C88" s="6">
         <f>VLOOKUP(B88,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4602,14 +4748,14 @@
         <v>75</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F88" s="6">
         <f>VLOOKUP(E88,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H88" s="6">
         <v>1</v>
@@ -4623,10 +4769,10 @@
     </row>
     <row r="89" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C89" s="6">
         <f>VLOOKUP(B89,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4636,7 +4782,7 @@
         <v>100</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F89" s="6">
         <f>VLOOKUP(E89,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4655,10 +4801,10 @@
     </row>
     <row r="90" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C90" s="6">
         <f>VLOOKUP(B90,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4668,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F90" s="6">
         <f>VLOOKUP(E90,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4687,10 +4833,10 @@
     </row>
     <row r="91" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C91" s="6">
         <f>VLOOKUP(B91,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4700,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F91" s="6">
         <f>VLOOKUP(E91,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4719,10 +4865,10 @@
     </row>
     <row r="92" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C92" s="6">
         <f>VLOOKUP(B92,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4732,7 +4878,7 @@
         <v>25</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F92" s="6">
         <f>VLOOKUP(E92,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4751,10 +4897,10 @@
     </row>
     <row r="93" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C93" s="6">
         <f>VLOOKUP(B93,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4764,7 +4910,7 @@
         <v>50</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F93" s="6">
         <f>VLOOKUP(E93,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4783,10 +4929,10 @@
     </row>
     <row r="94" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C94" s="6">
         <f>VLOOKUP(B94,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4796,14 +4942,14 @@
         <v>75</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F94" s="6">
         <f>VLOOKUP(E94,Overview!$F$9:$G$24,2,FALSE)</f>
         <v>7</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H94" s="6">
         <v>1</v>
@@ -4817,10 +4963,10 @@
     </row>
     <row r="95" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C95" s="6">
         <f>VLOOKUP(B95,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4830,7 +4976,7 @@
         <v>90</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F95" s="6">
         <f>VLOOKUP(E95,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4849,10 +4995,10 @@
     </row>
     <row r="96" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C96" s="6">
         <f>VLOOKUP(B96,Overview!$A$16:$B$20,2,FALSE)</f>
@@ -4862,7 +5008,7 @@
         <v>100</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F96" s="6">
         <f>VLOOKUP(E96,Overview!$F$9:$G$24,2,FALSE)</f>
@@ -4898,30 +5044,30 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">

--- a/ExcelToJSONConverter/excel/castle.xlsx
+++ b/ExcelToJSONConverter/excel/castle.xlsx
@@ -3,24 +3,24 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511B5976-3B30-4975-B92D-24819CE3B658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B51D18-CDD8-4DD3-90E1-77DACE4A7119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23160" yWindow="3105" windowWidth="16200" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="Castle" sheetId="4" r:id="rId2"/>
-    <sheet name="CastleRise" sheetId="3" r:id="rId3"/>
-    <sheet name="CastleMission" sheetId="5" r:id="rId4"/>
-    <sheet name="CastlePalace" sheetId="10" r:id="rId5"/>
-    <sheet name="CastleFarm" sheetId="11" r:id="rId6"/>
-    <sheet name="CastleMarket" sheetId="12" r:id="rId7"/>
-    <sheet name="CastleOffice" sheetId="14" r:id="rId8"/>
-    <sheet name="CastleMerchant" sheetId="15" r:id="rId9"/>
-    <sheet name="CastleGate" sheetId="13" r:id="rId10"/>
-    <sheet name="CastleMissionGrade" sheetId="8" r:id="rId11"/>
-    <sheet name="CastleMissionReward" sheetId="6" r:id="rId12"/>
-    <sheet name="CastleOfficeLevel" sheetId="9" r:id="rId13"/>
+    <sheet name="s_building" sheetId="4" r:id="rId2"/>
+    <sheet name="s_building_level" sheetId="3" r:id="rId3"/>
+    <sheet name="s_palace_effect" sheetId="10" r:id="rId4"/>
+    <sheet name="s_farm_effect" sheetId="11" r:id="rId5"/>
+    <sheet name="s_market_effect" sheetId="12" r:id="rId6"/>
+    <sheet name="s_gate_effect" sheetId="13" r:id="rId7"/>
+    <sheet name="s_office_effect" sheetId="14" r:id="rId8"/>
+    <sheet name="s_merchant_effect" sheetId="15" r:id="rId9"/>
+    <sheet name="s_office_mission" sheetId="5" r:id="rId10"/>
+    <sheet name="s_office_mission_grade" sheetId="8" r:id="rId11"/>
+    <sheet name="s_office_mission_reward_pool" sheetId="6" r:id="rId12"/>
+    <sheet name="s_office_level" sheetId="9" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="126">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -409,12 +409,6 @@
     <t>level_cap</t>
   </si>
   <si>
-    <t>time_stone_sec</t>
-  </si>
-  <si>
-    <t>ad_reduce_min</t>
-  </si>
-  <si>
     <t>rice_per_sec_base</t>
   </si>
   <si>
@@ -453,6 +447,12 @@
   </si>
   <si>
     <t>character_slot_max</t>
+  </si>
+  <si>
+    <t>save_time_time_stone</t>
+  </si>
+  <si>
+    <t>save_time_ad</t>
   </si>
 </sst>
 </file>
@@ -607,7 +607,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -640,9 +640,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1297,109 +1294,163 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D91FF98-8577-4206-85EC-A169AF2AE165}">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8633AE6D-7B52-48DE-9717-BAAA3077CF3B}">
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>102</v>
+    <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
-        <v>14</v>
+        <v>29</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
+        <v>32</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
-        <v>5400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
-        <v>5</v>
-      </c>
-      <c r="B7" s="15">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
-        <v>6</v>
-      </c>
-      <c r="B8" s="15">
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
-        <v>7</v>
-      </c>
-      <c r="B9" s="15">
-        <v>12600</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
-        <v>8</v>
-      </c>
-      <c r="B10" s="15">
-        <v>14400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
-        <v>9</v>
-      </c>
-      <c r="B11" s="15">
-        <v>16200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
-        <v>10</v>
-      </c>
-      <c r="B12" s="15">
-        <v>18000</v>
-      </c>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1622,8 +1673,8 @@
       <c r="I3" s="6">
         <v>200</v>
       </c>
-      <c r="J3" s="6">
-        <v>100</v>
+      <c r="J3" s="15">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1654,8 +1705,8 @@
       <c r="I4" s="6">
         <v>100</v>
       </c>
-      <c r="J4" s="6">
-        <v>100</v>
+      <c r="J4" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1686,8 +1737,8 @@
       <c r="I5" s="6">
         <v>1</v>
       </c>
-      <c r="J5" s="6">
-        <v>35</v>
+      <c r="J5" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1718,8 +1769,8 @@
       <c r="I6" s="6">
         <v>1</v>
       </c>
-      <c r="J6" s="6">
-        <v>30</v>
+      <c r="J6" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1750,8 +1801,8 @@
       <c r="I7" s="6">
         <v>1</v>
       </c>
-      <c r="J7" s="6">
-        <v>30</v>
+      <c r="J7" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1782,8 +1833,8 @@
       <c r="I8" s="6">
         <v>1</v>
       </c>
-      <c r="J8" s="6">
-        <v>30</v>
+      <c r="J8" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1816,8 +1867,8 @@
       <c r="I9" s="6">
         <v>1</v>
       </c>
-      <c r="J9" s="6">
-        <v>20</v>
+      <c r="J9" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1848,8 +1899,8 @@
       <c r="I10" s="6">
         <v>800</v>
       </c>
-      <c r="J10" s="6">
-        <v>100</v>
+      <c r="J10" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1880,8 +1931,8 @@
       <c r="I11" s="6">
         <v>400</v>
       </c>
-      <c r="J11" s="6">
-        <v>100</v>
+      <c r="J11" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1912,8 +1963,8 @@
       <c r="I12" s="6">
         <v>2</v>
       </c>
-      <c r="J12" s="6">
-        <v>40</v>
+      <c r="J12" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1944,8 +1995,8 @@
       <c r="I13" s="6">
         <v>1</v>
       </c>
-      <c r="J13" s="6">
-        <v>35</v>
+      <c r="J13" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1976,8 +2027,8 @@
       <c r="I14" s="6">
         <v>1</v>
       </c>
-      <c r="J14" s="6">
-        <v>35</v>
+      <c r="J14" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2008,8 +2059,8 @@
       <c r="I15" s="6">
         <v>1</v>
       </c>
-      <c r="J15" s="6">
-        <v>30</v>
+      <c r="J15" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2042,8 +2093,8 @@
       <c r="I16" s="6">
         <v>1</v>
       </c>
-      <c r="J16" s="6">
-        <v>30</v>
+      <c r="J16" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2074,8 +2125,8 @@
       <c r="I17" s="6">
         <v>1</v>
       </c>
-      <c r="J17" s="6">
-        <v>20</v>
+      <c r="J17" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2106,8 +2157,8 @@
       <c r="I18" s="6">
         <v>3000</v>
       </c>
-      <c r="J18" s="6">
-        <v>100</v>
+      <c r="J18" s="14">
+        <v>0.25</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2138,8 +2189,8 @@
       <c r="I19" s="6">
         <v>1500</v>
       </c>
-      <c r="J19" s="6">
-        <v>100</v>
+      <c r="J19" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2170,8 +2221,8 @@
       <c r="I20" s="6">
         <v>3</v>
       </c>
-      <c r="J20" s="6">
-        <v>40</v>
+      <c r="J20" s="14">
+        <v>0.15</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2202,8 +2253,8 @@
       <c r="I21" s="6">
         <v>1</v>
       </c>
-      <c r="J21" s="6">
-        <v>35</v>
+      <c r="J21" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2236,8 +2287,8 @@
       <c r="I22" s="6">
         <v>1</v>
       </c>
-      <c r="J22" s="6">
-        <v>25</v>
+      <c r="J22" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2268,8 +2319,8 @@
       <c r="I23" s="6">
         <v>1</v>
       </c>
-      <c r="J23" s="6">
-        <v>20</v>
+      <c r="J23" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2300,8 +2351,8 @@
       <c r="I24" s="6">
         <v>1</v>
       </c>
-      <c r="J24" s="6">
-        <v>15</v>
+      <c r="J24" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2332,8 +2383,8 @@
       <c r="I25" s="6">
         <v>200</v>
       </c>
-      <c r="J25" s="6">
-        <v>100</v>
+      <c r="J25" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2364,8 +2415,8 @@
       <c r="I26" s="6">
         <v>100</v>
       </c>
-      <c r="J26" s="6">
-        <v>100</v>
+      <c r="J26" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2396,8 +2447,8 @@
       <c r="I27" s="6">
         <v>1</v>
       </c>
-      <c r="J27" s="6">
-        <v>35</v>
+      <c r="J27" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2428,8 +2479,8 @@
       <c r="I28" s="6">
         <v>1</v>
       </c>
-      <c r="J28" s="6">
-        <v>30</v>
+      <c r="J28" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2462,8 +2513,8 @@
       <c r="I29" s="6">
         <v>1</v>
       </c>
-      <c r="J29" s="6">
-        <v>20</v>
+      <c r="J29" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2494,8 +2545,8 @@
       <c r="I30" s="6">
         <v>800</v>
       </c>
-      <c r="J30" s="6">
-        <v>100</v>
+      <c r="J30" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2526,8 +2577,8 @@
       <c r="I31" s="6">
         <v>400</v>
       </c>
-      <c r="J31" s="6">
-        <v>100</v>
+      <c r="J31" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2558,8 +2609,8 @@
       <c r="I32" s="6">
         <v>2</v>
       </c>
-      <c r="J32" s="6">
-        <v>40</v>
+      <c r="J32" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2590,8 +2641,8 @@
       <c r="I33" s="6">
         <v>1</v>
       </c>
-      <c r="J33" s="6">
-        <v>35</v>
+      <c r="J33" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2624,8 +2675,8 @@
       <c r="I34" s="6">
         <v>1</v>
       </c>
-      <c r="J34" s="6">
-        <v>30</v>
+      <c r="J34" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2656,8 +2707,8 @@
       <c r="I35" s="6">
         <v>1</v>
       </c>
-      <c r="J35" s="6">
-        <v>20</v>
+      <c r="J35" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2688,8 +2739,8 @@
       <c r="I36" s="6">
         <v>3000</v>
       </c>
-      <c r="J36" s="6">
-        <v>100</v>
+      <c r="J36" s="14">
+        <v>0.25</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2720,8 +2771,8 @@
       <c r="I37" s="6">
         <v>1500</v>
       </c>
-      <c r="J37" s="6">
-        <v>100</v>
+      <c r="J37" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2752,8 +2803,8 @@
       <c r="I38" s="6">
         <v>3</v>
       </c>
-      <c r="J38" s="6">
-        <v>40</v>
+      <c r="J38" s="14">
+        <v>0.15</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2784,8 +2835,8 @@
       <c r="I39" s="6">
         <v>1</v>
       </c>
-      <c r="J39" s="6">
-        <v>35</v>
+      <c r="J39" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2818,8 +2869,8 @@
       <c r="I40" s="6">
         <v>1</v>
       </c>
-      <c r="J40" s="6">
-        <v>25</v>
+      <c r="J40" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2850,8 +2901,8 @@
       <c r="I41" s="6">
         <v>1</v>
       </c>
-      <c r="J41" s="6">
-        <v>20</v>
+      <c r="J41" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2882,8 +2933,8 @@
       <c r="I42" s="6">
         <v>1</v>
       </c>
-      <c r="J42" s="6">
-        <v>15</v>
+      <c r="J42" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2914,8 +2965,8 @@
       <c r="I43" s="6">
         <v>200</v>
       </c>
-      <c r="J43" s="6">
-        <v>100</v>
+      <c r="J43" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2946,8 +2997,8 @@
       <c r="I44" s="6">
         <v>100</v>
       </c>
-      <c r="J44" s="6">
-        <v>100</v>
+      <c r="J44" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2978,8 +3029,8 @@
       <c r="I45" s="6">
         <v>1</v>
       </c>
-      <c r="J45" s="6">
-        <v>35</v>
+      <c r="J45" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3010,8 +3061,8 @@
       <c r="I46" s="6">
         <v>1</v>
       </c>
-      <c r="J46" s="6">
-        <v>30</v>
+      <c r="J46" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3044,8 +3095,8 @@
       <c r="I47" s="6">
         <v>1</v>
       </c>
-      <c r="J47" s="6">
-        <v>20</v>
+      <c r="J47" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3076,8 +3127,8 @@
       <c r="I48" s="6">
         <v>800</v>
       </c>
-      <c r="J48" s="6">
-        <v>100</v>
+      <c r="J48" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3108,8 +3159,8 @@
       <c r="I49" s="6">
         <v>400</v>
       </c>
-      <c r="J49" s="6">
-        <v>100</v>
+      <c r="J49" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3140,8 +3191,8 @@
       <c r="I50" s="6">
         <v>2</v>
       </c>
-      <c r="J50" s="6">
-        <v>40</v>
+      <c r="J50" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3172,8 +3223,8 @@
       <c r="I51" s="6">
         <v>1</v>
       </c>
-      <c r="J51" s="6">
-        <v>35</v>
+      <c r="J51" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3206,8 +3257,8 @@
       <c r="I52" s="6">
         <v>1</v>
       </c>
-      <c r="J52" s="6">
-        <v>30</v>
+      <c r="J52" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3238,8 +3289,8 @@
       <c r="I53" s="6">
         <v>1</v>
       </c>
-      <c r="J53" s="6">
-        <v>20</v>
+      <c r="J53" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3270,8 +3321,8 @@
       <c r="I54" s="6">
         <v>3000</v>
       </c>
-      <c r="J54" s="6">
-        <v>100</v>
+      <c r="J54" s="14">
+        <v>0.25</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3302,8 +3353,8 @@
       <c r="I55" s="6">
         <v>1500</v>
       </c>
-      <c r="J55" s="6">
-        <v>100</v>
+      <c r="J55" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3334,8 +3385,8 @@
       <c r="I56" s="6">
         <v>3</v>
       </c>
-      <c r="J56" s="6">
-        <v>40</v>
+      <c r="J56" s="14">
+        <v>0.15</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3366,8 +3417,8 @@
       <c r="I57" s="6">
         <v>1</v>
       </c>
-      <c r="J57" s="6">
-        <v>35</v>
+      <c r="J57" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3400,8 +3451,8 @@
       <c r="I58" s="6">
         <v>1</v>
       </c>
-      <c r="J58" s="6">
-        <v>25</v>
+      <c r="J58" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3432,8 +3483,8 @@
       <c r="I59" s="6">
         <v>1</v>
       </c>
-      <c r="J59" s="6">
-        <v>20</v>
+      <c r="J59" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3464,8 +3515,8 @@
       <c r="I60" s="6">
         <v>1</v>
       </c>
-      <c r="J60" s="6">
-        <v>15</v>
+      <c r="J60" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3496,8 +3547,8 @@
       <c r="I61" s="6">
         <v>200</v>
       </c>
-      <c r="J61" s="6">
-        <v>100</v>
+      <c r="J61" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3528,8 +3579,8 @@
       <c r="I62" s="6">
         <v>100</v>
       </c>
-      <c r="J62" s="6">
-        <v>100</v>
+      <c r="J62" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3560,8 +3611,8 @@
       <c r="I63" s="6">
         <v>1</v>
       </c>
-      <c r="J63" s="6">
-        <v>35</v>
+      <c r="J63" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3592,8 +3643,8 @@
       <c r="I64" s="6">
         <v>1</v>
       </c>
-      <c r="J64" s="6">
-        <v>30</v>
+      <c r="J64" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3626,8 +3677,8 @@
       <c r="I65" s="6">
         <v>1</v>
       </c>
-      <c r="J65" s="6">
-        <v>20</v>
+      <c r="J65" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3658,8 +3709,8 @@
       <c r="I66" s="6">
         <v>800</v>
       </c>
-      <c r="J66" s="6">
-        <v>100</v>
+      <c r="J66" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3690,8 +3741,8 @@
       <c r="I67" s="6">
         <v>400</v>
       </c>
-      <c r="J67" s="6">
-        <v>100</v>
+      <c r="J67" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3722,8 +3773,8 @@
       <c r="I68" s="6">
         <v>2</v>
       </c>
-      <c r="J68" s="6">
-        <v>40</v>
+      <c r="J68" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3754,8 +3805,8 @@
       <c r="I69" s="6">
         <v>1</v>
       </c>
-      <c r="J69" s="6">
-        <v>35</v>
+      <c r="J69" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3788,8 +3839,8 @@
       <c r="I70" s="6">
         <v>1</v>
       </c>
-      <c r="J70" s="6">
-        <v>30</v>
+      <c r="J70" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3820,8 +3871,8 @@
       <c r="I71" s="6">
         <v>1</v>
       </c>
-      <c r="J71" s="6">
-        <v>20</v>
+      <c r="J71" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3852,8 +3903,8 @@
       <c r="I72" s="6">
         <v>3000</v>
       </c>
-      <c r="J72" s="6">
-        <v>100</v>
+      <c r="J72" s="14">
+        <v>0.25</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3884,8 +3935,8 @@
       <c r="I73" s="6">
         <v>1500</v>
       </c>
-      <c r="J73" s="6">
-        <v>100</v>
+      <c r="J73" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3916,8 +3967,8 @@
       <c r="I74" s="6">
         <v>3</v>
       </c>
-      <c r="J74" s="6">
-        <v>40</v>
+      <c r="J74" s="14">
+        <v>0.15</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3948,8 +3999,8 @@
       <c r="I75" s="6">
         <v>1</v>
       </c>
-      <c r="J75" s="6">
-        <v>35</v>
+      <c r="J75" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3982,8 +4033,8 @@
       <c r="I76" s="6">
         <v>1</v>
       </c>
-      <c r="J76" s="6">
-        <v>25</v>
+      <c r="J76" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4014,8 +4065,8 @@
       <c r="I77" s="6">
         <v>1</v>
       </c>
-      <c r="J77" s="6">
-        <v>20</v>
+      <c r="J77" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4046,8 +4097,8 @@
       <c r="I78" s="6">
         <v>1</v>
       </c>
-      <c r="J78" s="6">
-        <v>15</v>
+      <c r="J78" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4078,8 +4129,8 @@
       <c r="I79" s="6">
         <v>200</v>
       </c>
-      <c r="J79" s="6">
-        <v>100</v>
+      <c r="J79" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4110,8 +4161,8 @@
       <c r="I80" s="6">
         <v>100</v>
       </c>
-      <c r="J80" s="6">
-        <v>100</v>
+      <c r="J80" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4142,8 +4193,8 @@
       <c r="I81" s="6">
         <v>1</v>
       </c>
-      <c r="J81" s="6">
-        <v>35</v>
+      <c r="J81" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4174,8 +4225,8 @@
       <c r="I82" s="6">
         <v>1</v>
       </c>
-      <c r="J82" s="6">
-        <v>30</v>
+      <c r="J82" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4208,8 +4259,8 @@
       <c r="I83" s="6">
         <v>1</v>
       </c>
-      <c r="J83" s="6">
-        <v>20</v>
+      <c r="J83" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4240,8 +4291,8 @@
       <c r="I84" s="6">
         <v>800</v>
       </c>
-      <c r="J84" s="6">
-        <v>100</v>
+      <c r="J84" s="14">
+        <v>0.3</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4272,8 +4323,8 @@
       <c r="I85" s="6">
         <v>400</v>
       </c>
-      <c r="J85" s="6">
-        <v>100</v>
+      <c r="J85" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4304,8 +4355,8 @@
       <c r="I86" s="6">
         <v>2</v>
       </c>
-      <c r="J86" s="6">
-        <v>40</v>
+      <c r="J86" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4336,8 +4387,8 @@
       <c r="I87" s="6">
         <v>1</v>
       </c>
-      <c r="J87" s="6">
-        <v>35</v>
+      <c r="J87" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4370,8 +4421,8 @@
       <c r="I88" s="6">
         <v>1</v>
       </c>
-      <c r="J88" s="6">
-        <v>30</v>
+      <c r="J88" s="14">
+        <v>0.4</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4402,8 +4453,8 @@
       <c r="I89" s="6">
         <v>1</v>
       </c>
-      <c r="J89" s="6">
-        <v>20</v>
+      <c r="J89" s="14">
+        <v>0.35</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4434,8 +4485,8 @@
       <c r="I90" s="6">
         <v>3000</v>
       </c>
-      <c r="J90" s="6">
-        <v>100</v>
+      <c r="J90" s="14">
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4466,8 +4517,8 @@
       <c r="I91" s="6">
         <v>1500</v>
       </c>
-      <c r="J91" s="6">
-        <v>100</v>
+      <c r="J91" s="14">
+        <v>0.2</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4498,8 +4549,8 @@
       <c r="I92" s="6">
         <v>3</v>
       </c>
-      <c r="J92" s="6">
-        <v>40</v>
+      <c r="J92" s="14">
+        <v>0.15</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4641,15 +4692,14 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D836302-B302-44BC-BDF2-498BD94CAC4F}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>102</v>
       </c>
@@ -4659,11 +4709,8 @@
       <c r="C1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>65</v>
       </c>
@@ -4673,11 +4720,8 @@
       <c r="C2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -4687,11 +4731,8 @@
       <c r="C3" s="6">
         <v>0</v>
       </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -4701,11 +4742,8 @@
       <c r="C4" s="6">
         <v>1200</v>
       </c>
-      <c r="D4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -4715,11 +4753,8 @@
       <c r="C5" s="6">
         <v>3600</v>
       </c>
-      <c r="D5" s="6">
-        <v>7200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -4729,11 +4764,8 @@
       <c r="C6" s="6">
         <v>8400</v>
       </c>
-      <c r="D6" s="6">
-        <v>43200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -4743,11 +4775,8 @@
       <c r="C7" s="6">
         <v>16800</v>
       </c>
-      <c r="D7" s="6">
-        <v>86400</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -4757,11 +4786,8 @@
       <c r="C8" s="6">
         <v>30000</v>
       </c>
-      <c r="D8" s="6">
-        <v>129600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -4771,11 +4797,8 @@
       <c r="C9" s="6">
         <v>48000</v>
       </c>
-      <c r="D9" s="6">
-        <v>172800</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -4785,11 +4808,8 @@
       <c r="C10" s="6">
         <v>70800</v>
       </c>
-      <c r="D10" s="6">
-        <v>259200</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -4799,11 +4819,8 @@
       <c r="C11" s="6">
         <v>102000</v>
       </c>
-      <c r="D11" s="6">
-        <v>345600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -4812,9 +4829,6 @@
       </c>
       <c r="C12" s="6">
         <v>144000</v>
-      </c>
-      <c r="D12" s="6">
-        <v>518400</v>
       </c>
     </row>
   </sheetData>
@@ -4947,7 +4961,7 @@
         <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>105</v>
@@ -4977,7 +4991,7 @@
       <c r="A3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>1</v>
       </c>
       <c r="C3" s="10">
@@ -4994,11 +5008,11 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="str">
+      <c r="A4" s="11" t="str">
         <f>A3</f>
         <v>NONE</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <f>B3+1</f>
         <v>2</v>
       </c>
@@ -5016,11 +5030,11 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="str">
+      <c r="A5" s="11" t="str">
         <f>A4</f>
         <v>NONE</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <f>B4+1</f>
         <v>3</v>
       </c>
@@ -5038,11 +5052,11 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="str">
+      <c r="A6" s="11" t="str">
         <f t="shared" ref="A6:A12" si="0">A5</f>
         <v>NONE</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f t="shared" ref="B6:B12" si="1">B5+1</f>
         <v>4</v>
       </c>
@@ -5060,11 +5074,11 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="str">
+      <c r="A7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NONE</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -5082,11 +5096,11 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="str">
+      <c r="A8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NONE</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -5104,11 +5118,11 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="str">
+      <c r="A9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NONE</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -5126,11 +5140,11 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="str">
+      <c r="A10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NONE</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -5148,11 +5162,11 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="str">
+      <c r="A11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NONE</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -5170,11 +5184,11 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="str">
+      <c r="A12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>NONE</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -5195,7 +5209,7 @@
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>1</v>
       </c>
       <c r="C13" s="10">
@@ -5215,7 +5229,7 @@
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <f>B13+1</f>
         <v>2</v>
       </c>
@@ -5236,7 +5250,7 @@
       <c r="A15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <f>B14+1</f>
         <v>3</v>
       </c>
@@ -5257,7 +5271,7 @@
       <c r="A16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <f t="shared" ref="B16:B22" si="2">B15+1</f>
         <v>4</v>
       </c>
@@ -5278,7 +5292,7 @@
       <c r="A17" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
@@ -5299,7 +5313,7 @@
       <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -5320,7 +5334,7 @@
       <c r="A19" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -5341,7 +5355,7 @@
       <c r="A20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -5362,7 +5376,7 @@
       <c r="A21" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -5383,7 +5397,7 @@
       <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -5411,163 +5425,183 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8633AE6D-7B52-48DE-9717-BAAA3077CF3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13DC9EEB-7773-411B-BE55-63D7D306AC3A}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>28</v>
+      <c r="A1" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6">
         <v>30</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6">
         <v>33</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6">
         <v>36</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6">
         <v>39</v>
       </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="14">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6">
+        <v>14</v>
+      </c>
+      <c r="D7" s="6">
         <v>42</v>
       </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="6">
-        <v>3</v>
-      </c>
-      <c r="D7" s="7"/>
     </row>
     <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>47</v>
+      <c r="A8" s="14">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6">
+        <v>6</v>
       </c>
       <c r="C8" s="6">
-        <v>3</v>
-      </c>
-      <c r="D8" s="7"/>
+        <v>15</v>
+      </c>
+      <c r="D8" s="6">
+        <v>45</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="14">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6">
+        <v>16</v>
+      </c>
+      <c r="D9" s="6">
         <v>48</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="14">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>17</v>
+      </c>
+      <c r="D10" s="6">
         <v>52</v>
       </c>
-      <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>54</v>
+      <c r="A11" s="14">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6">
+        <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>4</v>
-      </c>
-      <c r="D11" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="D11" s="6">
+        <v>56</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>57</v>
+      <c r="A12" s="14">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6">
+        <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="D12" s="6">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -5577,192 +5611,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13DC9EEB-7773-411B-BE55-63D7D306AC3A}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="6">
-        <v>10</v>
-      </c>
-      <c r="D3" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6">
-        <v>11</v>
-      </c>
-      <c r="D4" s="6">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6">
-        <v>12</v>
-      </c>
-      <c r="D5" s="6">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6">
-        <v>13</v>
-      </c>
-      <c r="D6" s="6">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6">
-        <v>5</v>
-      </c>
-      <c r="C7" s="6">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6">
-        <v>6</v>
-      </c>
-      <c r="C8" s="6">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6">
-        <v>17</v>
-      </c>
-      <c r="D10" s="6">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>18</v>
-      </c>
-      <c r="D11" s="6">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
-        <v>10</v>
-      </c>
-      <c r="B12" s="6">
-        <v>10</v>
-      </c>
-      <c r="C12" s="6">
-        <v>20</v>
-      </c>
-      <c r="D12" s="6">
-        <v>60</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{319D2D76-D91C-4464-9ACC-9F45A7C3CE4A}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5773,18 +5621,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>102</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -5795,21 +5643,21 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15">
         <v>5</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="16">
         <v>5000</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
         <v>60</v>
       </c>
       <c r="C4" s="6">
@@ -5817,10 +5665,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>115</v>
       </c>
       <c r="C5" s="6">
@@ -5828,10 +5676,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>170</v>
       </c>
       <c r="C6" s="6">
@@ -5839,10 +5687,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>5</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>225</v>
       </c>
       <c r="C7" s="6">
@@ -5850,10 +5698,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>6</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>280</v>
       </c>
       <c r="C8" s="6">
@@ -5861,10 +5709,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>335</v>
       </c>
       <c r="C9" s="6">
@@ -5872,10 +5720,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>390</v>
       </c>
       <c r="C10" s="6">
@@ -5883,10 +5731,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>9</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>445</v>
       </c>
       <c r="C11" s="6">
@@ -5894,10 +5742,10 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>10</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>500</v>
       </c>
       <c r="C12" s="6">
@@ -5911,7 +5759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A903481-2A22-4208-BA94-7D013AB4AE41}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5922,18 +5770,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>115</v>
+      <c r="B1" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -5944,21 +5792,21 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15">
         <v>0.5</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="16">
         <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
         <v>6</v>
       </c>
       <c r="C4" s="6">
@@ -5966,10 +5814,10 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>11.5</v>
       </c>
       <c r="C5" s="6">
@@ -5977,10 +5825,10 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>17</v>
       </c>
       <c r="C6" s="6">
@@ -5988,10 +5836,10 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>5</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>22.5</v>
       </c>
       <c r="C7" s="6">
@@ -5999,10 +5847,10 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>6</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>28</v>
       </c>
       <c r="C8" s="6">
@@ -6010,10 +5858,10 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>33.5</v>
       </c>
       <c r="C9" s="6">
@@ -6021,10 +5869,10 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>39</v>
       </c>
       <c r="C10" s="6">
@@ -6032,10 +5880,10 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>9</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>44.5</v>
       </c>
       <c r="C11" s="6">
@@ -6043,14 +5891,126 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>10</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>50</v>
       </c>
       <c r="C12" s="6">
         <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D91FF98-8577-4206-85EC-A169AF2AE165}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="14">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="14">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="14">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="14">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="14">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14">
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="14">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14">
+        <v>18000</v>
       </c>
     </row>
   </sheetData>
@@ -6073,27 +6033,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -6107,27 +6067,27 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15">
         <v>3</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="16">
         <v>90</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <v>9</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
         <v>3</v>
       </c>
       <c r="C4" s="6">
@@ -6141,10 +6101,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>4</v>
       </c>
       <c r="C5" s="6">
@@ -6158,10 +6118,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>5</v>
       </c>
       <c r="C6" s="6">
@@ -6175,10 +6135,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>5</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>6</v>
       </c>
       <c r="C7" s="6">
@@ -6192,10 +6152,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>6</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>6</v>
       </c>
       <c r="C8" s="6">
@@ -6209,10 +6169,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>7</v>
       </c>
       <c r="C9" s="6">
@@ -6226,10 +6186,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>8</v>
       </c>
       <c r="C10" s="6">
@@ -6243,10 +6203,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>9</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>9</v>
       </c>
       <c r="C11" s="6">
@@ -6260,10 +6220,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>10</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>10</v>
       </c>
       <c r="C12" s="6">
@@ -6295,24 +6255,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="2" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -6323,24 +6283,24 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16">
+      <c r="A3" s="14">
+        <v>1</v>
+      </c>
+      <c r="B3" s="15">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C3" s="17">
-        <v>0</v>
-      </c>
-      <c r="D3" s="17">
+      <c r="C3" s="16">
+        <v>0</v>
+      </c>
+      <c r="D3" s="16">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="C4" s="6">
@@ -6351,10 +6311,10 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>3</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="C5" s="6">
@@ -6365,10 +6325,10 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>1.15E-2</v>
       </c>
       <c r="C6" s="6">
@@ -6379,10 +6339,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>5</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>1.4E-2</v>
       </c>
       <c r="C7" s="6">
@@ -6393,10 +6353,10 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>6</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>1.6E-2</v>
       </c>
       <c r="C8" s="6">
@@ -6407,10 +6367,10 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>7</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>1.8499999999999999E-2</v>
       </c>
       <c r="C9" s="6">
@@ -6421,10 +6381,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>8</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>2.0500000000000001E-2</v>
       </c>
       <c r="C10" s="6">
@@ -6435,10 +6395,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>9</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>2.3E-2</v>
       </c>
       <c r="C11" s="6">
@@ -6449,10 +6409,10 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>10</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="C12" s="6">
